--- a/doc/TPI_G7_Crisantemo.xlsx
+++ b/doc/TPI_G7_Crisantemo.xlsx
@@ -5,6 +5,7 @@
   <sheets>
     <sheet state="visible" name="Matrices de decisión" sheetId="1" r:id="rId5"/>
     <sheet state="visible" name="Critic" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="Entropia" sheetId="3" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -12,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="86">
   <si>
     <t>Dificultad de Elaboración</t>
   </si>
@@ -74,12 +75,6 @@
     </r>
   </si>
   <si>
-    <t>Max</t>
-  </si>
-  <si>
-    <t>Min</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <rFont val="Arial"/>
@@ -98,103 +93,6 @@
     </r>
   </si>
   <si>
-    <t>Demanda Esperada</t>
-  </si>
-  <si>
-    <t>Rentabilidad (Pesos Uruguayos)</t>
-  </si>
-  <si>
-    <t>Tiempo de Elaboración (Por Lote) en Minutos</t>
-  </si>
-  <si>
-    <t>Dificultad de elaboración</t>
-  </si>
-  <si>
-    <t>Vida útil</t>
-  </si>
-  <si>
-    <t>Desperdicio Esperado</t>
-  </si>
-  <si>
-    <t>Contribución de variedad a la vitrina</t>
-  </si>
-  <si>
-    <t>A1</t>
-  </si>
-  <si>
-    <t>1°</t>
-  </si>
-  <si>
-    <t>Scones</t>
-  </si>
-  <si>
-    <t>2°</t>
-  </si>
-  <si>
-    <t>A2</t>
-  </si>
-  <si>
-    <t>Chipá</t>
-  </si>
-  <si>
-    <t>A3</t>
-  </si>
-  <si>
-    <t>Roll de Canela</t>
-  </si>
-  <si>
-    <t>A4</t>
-  </si>
-  <si>
-    <t>Porción de Tarta de coco</t>
-  </si>
-  <si>
-    <t>Tabla AHP</t>
-  </si>
-  <si>
-    <t>A5</t>
-  </si>
-  <si>
-    <t>Alfajor de Dulce de Leche</t>
-  </si>
-  <si>
-    <t>A6</t>
-  </si>
-  <si>
-    <t>Alfajor de Frutos Rojos</t>
-  </si>
-  <si>
-    <t>Promedio (W)</t>
-  </si>
-  <si>
-    <t>A7</t>
-  </si>
-  <si>
-    <t>Cookies</t>
-  </si>
-  <si>
-    <t>N
-(Alternativas)</t>
-  </si>
-  <si>
-    <t>AW</t>
-  </si>
-  <si>
-    <t>AW/Wi</t>
-  </si>
-  <si>
-    <t>A8</t>
-  </si>
-  <si>
-    <t>Porción de Brownie</t>
-  </si>
-  <si>
-    <t>A9</t>
-  </si>
-  <si>
-    <t>Porción de Tarta de Ricota</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <rFont val="Arial"/>
@@ -213,6 +111,15 @@
     </r>
   </si>
   <si>
+    <t>Max</t>
+  </si>
+  <si>
+    <t>Min</t>
+  </si>
+  <si>
+    <t>1°</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <rFont val="Arial"/>
@@ -231,6 +138,172 @@
     </r>
   </si>
   <si>
+    <t>Demanda Esperada</t>
+  </si>
+  <si>
+    <t>Rentabilidad (Pesos Uruguayos)</t>
+  </si>
+  <si>
+    <t>Tiempo de Elaboración (Por Lote) en Minutos</t>
+  </si>
+  <si>
+    <t>Dificultad de elaboración</t>
+  </si>
+  <si>
+    <t>2°</t>
+  </si>
+  <si>
+    <t>Vida útil</t>
+  </si>
+  <si>
+    <t>Desperdicio Esperado</t>
+  </si>
+  <si>
+    <t>Contribución de variedad a la vitrina</t>
+  </si>
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Matriz de Decisión Normalizada</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">
+(Productos Habituales)</t>
+    </r>
+  </si>
+  <si>
+    <t>Scones</t>
+  </si>
+  <si>
+    <t>Tabla AHP</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Matriz de Decisión </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">
+(Productos Habituales)</t>
+    </r>
+  </si>
+  <si>
+    <t>Promedio (W)</t>
+  </si>
+  <si>
+    <t>N
+(Alternativas)</t>
+  </si>
+  <si>
+    <t>AW</t>
+  </si>
+  <si>
+    <t>A2</t>
+  </si>
+  <si>
+    <t>AW/Wi</t>
+  </si>
+  <si>
+    <t>Chipá</t>
+  </si>
+  <si>
+    <t>A3</t>
+  </si>
+  <si>
+    <t>Roll de Canela</t>
+  </si>
+  <si>
+    <t>A4</t>
+  </si>
+  <si>
+    <t>Porción de Tarta de coco</t>
+  </si>
+  <si>
+    <t>A5</t>
+  </si>
+  <si>
+    <t>Alfajor de Dulce de Leche</t>
+  </si>
+  <si>
+    <t>A6</t>
+  </si>
+  <si>
+    <t>Alfajor de Frutos Rojos</t>
+  </si>
+  <si>
+    <t>A7</t>
+  </si>
+  <si>
+    <t>Cookies</t>
+  </si>
+  <si>
+    <t>A8</t>
+  </si>
+  <si>
+    <t>Porción de Brownie</t>
+  </si>
+  <si>
+    <t>A9</t>
+  </si>
+  <si>
+    <t>Porción de Tarta de Ricota</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Matriz de Decisión </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">
+(Productos Habituales)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Matriz de Decisión </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">
+(Productos Habituales)</t>
+    </r>
+  </si>
+  <si>
     <t>C1</t>
   </si>
   <si>
@@ -255,25 +328,10 @@
     <t>SUMA</t>
   </si>
   <si>
-    <t>1-CJK</t>
-  </si>
-  <si>
-    <t>MAX</t>
-  </si>
-  <si>
-    <t>DESV EST</t>
-  </si>
-  <si>
     <t>λ</t>
   </si>
   <si>
-    <t>MIN</t>
-  </si>
-  <si>
     <t>IC = (λ - n) / (n-1)</t>
-  </si>
-  <si>
-    <t>AMPLITUD</t>
   </si>
   <si>
     <t xml:space="preserve">IA </t>
@@ -309,13 +367,19 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
+    <t>1-CJK</t>
+  </si>
+  <si>
+    <t>MAX</t>
+  </si>
+  <si>
     <t>A10</t>
   </si>
   <si>
-    <t>DJ</t>
-  </si>
-  <si>
     <t>Shio Pan</t>
+  </si>
+  <si>
+    <t>DESV EST</t>
   </si>
   <si>
     <r>
@@ -336,10 +400,28 @@
     </r>
   </si>
   <si>
+    <t>MIN</t>
+  </si>
+  <si>
+    <t>AMPLITUD</t>
+  </si>
+  <si>
+    <t>Alfajor de Maní</t>
+  </si>
+  <si>
+    <t>HJ</t>
+  </si>
+  <si>
+    <t>DJ</t>
+  </si>
+  <si>
     <t>WJ</t>
   </si>
   <si>
-    <t>Alfajor de Maní</t>
+    <t>k</t>
+  </si>
+  <si>
+    <t>Cant. Alternativas</t>
   </si>
 </sst>
 </file>
@@ -493,7 +575,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="42">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -511,28 +593,28 @@
     <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
+    <xf borderId="2" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
     <xf borderId="6" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="7" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="2" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center"/>
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="2" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf borderId="2" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -543,6 +625,12 @@
     <xf borderId="2" fillId="0" fontId="2" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
+    <xf borderId="2" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
     <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="2" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
@@ -550,13 +638,7 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
     <xf borderId="8" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="2" fillId="0" fontId="2" numFmtId="165" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
@@ -566,26 +648,42 @@
     <xf borderId="2" fillId="0" fontId="2" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
+    <xf borderId="2" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="2" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
     <xf borderId="2" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="2" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="9" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="2" fillId="0" fontId="2" numFmtId="166" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="2" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="2" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="9" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf borderId="2" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="166" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="2" fillId="0" fontId="2" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf borderId="2" fillId="5" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -599,6 +697,10 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -903,187 +1005,187 @@
     </row>
     <row r="8">
       <c r="B8" s="4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="L8" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="M8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="N8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="O8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="R8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="T8" s="11"/>
+      <c r="U8" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="V8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="W8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="X8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="AA8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC8" s="11"/>
+      <c r="AD8" s="11"/>
+      <c r="AE8" s="11"/>
+      <c r="AF8" s="11"/>
+      <c r="AG8" s="11"/>
+      <c r="AH8" s="11"/>
+      <c r="AI8" s="11"/>
+    </row>
+    <row r="9">
+      <c r="B9" s="8"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="M8" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="N8" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="O8" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="P8" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q8" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="R8" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="S8" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="T8" s="12"/>
-      <c r="U8" s="11" t="s">
+      <c r="I9" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J9" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="V8" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="W8" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="X8" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y8" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="Z8" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="AA8" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="AB8" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="AC8" s="12"/>
-      <c r="AD8" s="12"/>
-      <c r="AE8" s="12"/>
-      <c r="AF8" s="12"/>
-      <c r="AG8" s="12"/>
-      <c r="AH8" s="12"/>
-      <c r="AI8" s="12"/>
-    </row>
-    <row r="9">
-      <c r="B9" s="7"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="G9" s="9" t="s">
+      <c r="L9" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="M9" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="N9" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="I9" s="9" t="s">
+      <c r="O9" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="J9" s="9" t="s">
+      <c r="P9" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="L9" s="14" t="s">
+      <c r="Q9" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="R9" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="S9" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="T9" s="14"/>
+      <c r="U9" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="V9" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="W9" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="X9" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y9" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z9" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA9" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB9" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="AC9" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="AD9" s="14"/>
+      <c r="AE9" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="M9" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="N9" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="O9" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="P9" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q9" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="R9" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="S9" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="T9" s="15"/>
-      <c r="U9" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="V9" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="W9" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="X9" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="Y9" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="Z9" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="AA9" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="AB9" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="AC9" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="AD9" s="15"/>
-      <c r="AE9" s="16" t="s">
-        <v>43</v>
-      </c>
       <c r="AF9" s="16" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AG9" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="AH9" s="15"/>
-      <c r="AI9" s="15"/>
+        <v>38</v>
+      </c>
+      <c r="AH9" s="14"/>
+      <c r="AI9" s="14"/>
     </row>
     <row r="10">
-      <c r="B10" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>27</v>
+      <c r="B10" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="D10" s="6">
         <v>18.0</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="15">
         <f>75-17</f>
         <v>58</v>
       </c>
@@ -1102,8 +1204,8 @@
       <c r="J10" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="L10" s="9" t="s">
-        <v>18</v>
+      <c r="L10" s="10" t="s">
+        <v>21</v>
       </c>
       <c r="M10" s="17">
         <v>1.0</v>
@@ -1129,43 +1231,43 @@
       <c r="S10" s="17">
         <v>1.0</v>
       </c>
-      <c r="T10" s="12"/>
-      <c r="U10" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="V10" s="22">
+      <c r="T10" s="11"/>
+      <c r="U10" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="V10" s="19">
         <f t="shared" ref="V10:V16" si="2">M10/$M$17</f>
         <v>0.04347826087</v>
       </c>
-      <c r="W10" s="22">
+      <c r="W10" s="19">
         <f t="shared" ref="W10:W16" si="3">N10/$N$17</f>
         <v>0.04</v>
       </c>
-      <c r="X10" s="22">
+      <c r="X10" s="19">
         <f t="shared" ref="X10:X16" si="4">O10/$O$17</f>
         <v>0.1042011247</v>
       </c>
-      <c r="Y10" s="22">
+      <c r="Y10" s="19">
         <f t="shared" ref="Y10:AB10" si="1">P10/P$17</f>
         <v>0.0093708166</v>
       </c>
-      <c r="Z10" s="22">
+      <c r="Z10" s="19">
         <f t="shared" si="1"/>
         <v>0.05785123967</v>
       </c>
-      <c r="AA10" s="22">
+      <c r="AA10" s="19">
         <f t="shared" si="1"/>
         <v>0.008695652174</v>
       </c>
-      <c r="AB10" s="22">
+      <c r="AB10" s="19">
         <f t="shared" si="1"/>
         <v>0.0303030303</v>
       </c>
-      <c r="AC10" s="24">
+      <c r="AC10" s="20">
         <f t="shared" ref="AC10:AC16" si="6">AVERAGE(V10:AB10)</f>
         <v>0.04198573205</v>
       </c>
-      <c r="AD10" s="12"/>
+      <c r="AD10" s="11"/>
       <c r="AE10" s="6">
         <v>7.0</v>
       </c>
@@ -1177,20 +1279,20 @@
         <f t="shared" ref="AG10:AG16" si="7">AF10/AC10</f>
         <v>12.44693803</v>
       </c>
-      <c r="AH10" s="12"/>
-      <c r="AI10" s="12"/>
+      <c r="AH10" s="11"/>
+      <c r="AI10" s="11"/>
     </row>
     <row r="11">
-      <c r="B11" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>30</v>
+      <c r="B11" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>39</v>
       </c>
       <c r="D11" s="6">
         <v>9.0</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="15">
         <f>100-25</f>
         <v>75</v>
       </c>
@@ -1209,8 +1311,8 @@
       <c r="J11" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="L11" s="9" t="s">
-        <v>19</v>
+      <c r="L11" s="10" t="s">
+        <v>22</v>
       </c>
       <c r="M11" s="17">
         <v>7.0</v>
@@ -1233,44 +1335,44 @@
       <c r="S11" s="17">
         <v>7.0</v>
       </c>
-      <c r="T11" s="12"/>
-      <c r="U11" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="V11" s="22">
+      <c r="T11" s="11"/>
+      <c r="U11" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="V11" s="19">
         <f t="shared" si="2"/>
         <v>0.3043478261</v>
       </c>
-      <c r="W11" s="22">
+      <c r="W11" s="19">
         <f t="shared" si="3"/>
         <v>0.28</v>
       </c>
-      <c r="X11" s="22">
+      <c r="X11" s="19">
         <f t="shared" si="4"/>
         <v>0.729407873</v>
       </c>
-      <c r="Y11" s="22">
+      <c r="Y11" s="19">
         <f t="shared" ref="Y11:AB11" si="5">P11/P$17</f>
         <v>0.327978581</v>
       </c>
-      <c r="Z11" s="22">
+      <c r="Z11" s="19">
         <f t="shared" si="5"/>
         <v>0.05785123967</v>
       </c>
-      <c r="AA11" s="22">
+      <c r="AA11" s="19">
         <f t="shared" si="5"/>
         <v>0.06086956522</v>
       </c>
-      <c r="AB11" s="22">
+      <c r="AB11" s="19">
         <f t="shared" si="5"/>
         <v>0.2121212121</v>
       </c>
-      <c r="AC11" s="24">
+      <c r="AC11" s="20">
         <f t="shared" si="6"/>
         <v>0.2817966139</v>
       </c>
-      <c r="AD11" s="12"/>
-      <c r="AE11" s="12"/>
+      <c r="AD11" s="11"/>
+      <c r="AE11" s="11"/>
       <c r="AF11" s="6">
         <v>3.381005025302969</v>
       </c>
@@ -1278,20 +1380,20 @@
         <f t="shared" si="7"/>
         <v>11.99803283</v>
       </c>
-      <c r="AH11" s="12"/>
-      <c r="AI11" s="12"/>
+      <c r="AH11" s="11"/>
+      <c r="AI11" s="11"/>
     </row>
     <row r="12">
-      <c r="B12" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>32</v>
+      <c r="B12" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>41</v>
       </c>
       <c r="D12" s="6">
         <v>6.0</v>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="15">
         <f>180-30</f>
         <v>150</v>
       </c>
@@ -1310,8 +1412,8 @@
       <c r="J12" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="L12" s="9" t="s">
-        <v>20</v>
+      <c r="L12" s="10" t="s">
+        <v>23</v>
       </c>
       <c r="M12" s="17">
         <v>1.0</v>
@@ -1335,44 +1437,44 @@
       <c r="S12" s="17">
         <v>9.0</v>
       </c>
-      <c r="T12" s="12"/>
-      <c r="U12" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="V12" s="22">
+      <c r="T12" s="11"/>
+      <c r="U12" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="V12" s="19">
         <f t="shared" si="2"/>
         <v>0.04347826087</v>
       </c>
-      <c r="W12" s="22">
+      <c r="W12" s="19">
         <f t="shared" si="3"/>
         <v>0.04</v>
       </c>
-      <c r="X12" s="22">
+      <c r="X12" s="19">
         <f t="shared" si="4"/>
         <v>0.1042011247</v>
       </c>
-      <c r="Y12" s="22">
+      <c r="Y12" s="19">
         <f t="shared" ref="Y12:AB12" si="8">P12/P$17</f>
         <v>0.234270415</v>
       </c>
-      <c r="Z12" s="22">
+      <c r="Z12" s="19">
         <f t="shared" si="8"/>
         <v>0.4049586777</v>
       </c>
-      <c r="AA12" s="22">
+      <c r="AA12" s="19">
         <f t="shared" si="8"/>
         <v>0.4260869565</v>
       </c>
-      <c r="AB12" s="22">
+      <c r="AB12" s="19">
         <f t="shared" si="8"/>
         <v>0.2727272727</v>
       </c>
-      <c r="AC12" s="24">
+      <c r="AC12" s="20">
         <f t="shared" si="6"/>
         <v>0.2179603868</v>
       </c>
-      <c r="AD12" s="12"/>
-      <c r="AE12" s="12"/>
+      <c r="AD12" s="11"/>
+      <c r="AE12" s="11"/>
       <c r="AF12" s="6">
         <v>3.3423266260485875</v>
       </c>
@@ -1380,20 +1482,20 @@
         <f t="shared" si="7"/>
         <v>15.33455999</v>
       </c>
-      <c r="AH12" s="12"/>
-      <c r="AI12" s="12"/>
+      <c r="AH12" s="11"/>
+      <c r="AI12" s="11"/>
     </row>
     <row r="13">
-      <c r="B13" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>34</v>
+      <c r="B13" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>43</v>
       </c>
       <c r="D13" s="6">
         <v>4.0</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="15">
         <f>220-52</f>
         <v>168</v>
       </c>
@@ -1412,8 +1514,8 @@
       <c r="J13" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="L13" s="9" t="s">
-        <v>21</v>
+      <c r="L13" s="10" t="s">
+        <v>24</v>
       </c>
       <c r="M13" s="17">
         <v>5.0</v>
@@ -1439,44 +1541,44 @@
       <c r="S13" s="17">
         <v>1.0</v>
       </c>
-      <c r="T13" s="12"/>
-      <c r="U13" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="V13" s="22">
+      <c r="T13" s="11"/>
+      <c r="U13" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="V13" s="19">
         <f t="shared" si="2"/>
         <v>0.2173913043</v>
       </c>
-      <c r="W13" s="22">
+      <c r="W13" s="19">
         <f t="shared" si="3"/>
         <v>0.04</v>
       </c>
-      <c r="X13" s="22">
+      <c r="X13" s="19">
         <f t="shared" si="4"/>
         <v>0.02084022494</v>
       </c>
-      <c r="Y13" s="22">
+      <c r="Y13" s="19">
         <f t="shared" ref="Y13:AB13" si="10">P13/P$17</f>
         <v>0.046854083</v>
       </c>
-      <c r="Z13" s="22">
+      <c r="Z13" s="19">
         <f t="shared" si="10"/>
         <v>0.4049586777</v>
       </c>
-      <c r="AA13" s="22">
+      <c r="AA13" s="19">
         <f t="shared" si="10"/>
         <v>0.008695652174</v>
       </c>
-      <c r="AB13" s="22">
+      <c r="AB13" s="19">
         <f t="shared" si="10"/>
         <v>0.0303030303</v>
       </c>
-      <c r="AC13" s="24">
+      <c r="AC13" s="20">
         <f t="shared" si="6"/>
         <v>0.1098632818</v>
       </c>
-      <c r="AD13" s="12"/>
-      <c r="AE13" s="12"/>
+      <c r="AD13" s="11"/>
+      <c r="AE13" s="11"/>
       <c r="AF13" s="6">
         <v>1.4964450358269046</v>
       </c>
@@ -1484,20 +1586,20 @@
         <f t="shared" si="7"/>
         <v>13.62097519</v>
       </c>
-      <c r="AH13" s="12"/>
-      <c r="AI13" s="12"/>
+      <c r="AH13" s="11"/>
+      <c r="AI13" s="11"/>
     </row>
     <row r="14">
-      <c r="B14" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>37</v>
+      <c r="B14" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>45</v>
       </c>
       <c r="D14" s="6">
         <v>6.0</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="15">
         <f>140 - 58</f>
         <v>82</v>
       </c>
@@ -1516,8 +1618,8 @@
       <c r="J14" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="L14" s="9" t="s">
-        <v>22</v>
+      <c r="L14" s="10" t="s">
+        <v>26</v>
       </c>
       <c r="M14" s="17">
         <v>1.0</v>
@@ -1542,44 +1644,44 @@
       <c r="S14" s="17">
         <v>7.0</v>
       </c>
-      <c r="T14" s="12"/>
-      <c r="U14" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="V14" s="22">
+      <c r="T14" s="11"/>
+      <c r="U14" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="V14" s="19">
         <f t="shared" si="2"/>
         <v>0.04347826087</v>
       </c>
-      <c r="W14" s="22">
+      <c r="W14" s="19">
         <f t="shared" si="3"/>
         <v>0.28</v>
       </c>
-      <c r="X14" s="22">
+      <c r="X14" s="19">
         <f t="shared" si="4"/>
         <v>0.01488587496</v>
       </c>
-      <c r="Y14" s="22">
+      <c r="Y14" s="19">
         <f t="shared" ref="Y14:AB14" si="11">P14/P$17</f>
         <v>0.006693440428</v>
       </c>
-      <c r="Z14" s="22">
+      <c r="Z14" s="19">
         <f t="shared" si="11"/>
         <v>0.05785123967</v>
       </c>
-      <c r="AA14" s="22">
+      <c r="AA14" s="19">
         <f t="shared" si="11"/>
         <v>0.4260869565</v>
       </c>
-      <c r="AB14" s="22">
+      <c r="AB14" s="19">
         <f t="shared" si="11"/>
         <v>0.2121212121</v>
       </c>
-      <c r="AC14" s="24">
+      <c r="AC14" s="20">
         <f t="shared" si="6"/>
         <v>0.1487309978</v>
       </c>
-      <c r="AD14" s="12"/>
-      <c r="AE14" s="12"/>
+      <c r="AD14" s="11"/>
+      <c r="AE14" s="11"/>
       <c r="AF14" s="6">
         <v>1.916986210445512</v>
       </c>
@@ -1587,20 +1689,20 @@
         <f t="shared" si="7"/>
         <v>12.88894877</v>
       </c>
-      <c r="AH14" s="12"/>
-      <c r="AI14" s="12"/>
+      <c r="AH14" s="11"/>
+      <c r="AI14" s="11"/>
     </row>
     <row r="15">
-      <c r="B15" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>39</v>
+      <c r="B15" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>47</v>
       </c>
       <c r="D15" s="6">
         <v>6.0</v>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="15">
         <f>140 - 54</f>
         <v>86</v>
       </c>
@@ -1619,8 +1721,8 @@
       <c r="J15" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="L15" s="9" t="s">
-        <v>23</v>
+      <c r="L15" s="10" t="s">
+        <v>27</v>
       </c>
       <c r="M15" s="17">
         <v>7.0</v>
@@ -1647,44 +1749,44 @@
       <c r="S15" s="17">
         <v>7.0</v>
       </c>
-      <c r="T15" s="12"/>
-      <c r="U15" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="V15" s="22">
+      <c r="T15" s="11"/>
+      <c r="U15" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="V15" s="19">
         <f t="shared" si="2"/>
         <v>0.3043478261</v>
       </c>
-      <c r="W15" s="22">
+      <c r="W15" s="19">
         <f t="shared" si="3"/>
         <v>0.28</v>
       </c>
-      <c r="X15" s="22">
+      <c r="X15" s="19">
         <f t="shared" si="4"/>
         <v>0.01488587496</v>
       </c>
-      <c r="Y15" s="22">
+      <c r="Y15" s="19">
         <f t="shared" ref="Y15:AB15" si="12">P15/P$17</f>
         <v>0.327978581</v>
       </c>
-      <c r="Z15" s="22">
+      <c r="Z15" s="19">
         <f t="shared" si="12"/>
         <v>0.00826446281</v>
       </c>
-      <c r="AA15" s="22">
+      <c r="AA15" s="19">
         <f t="shared" si="12"/>
         <v>0.06086956522</v>
       </c>
-      <c r="AB15" s="22">
+      <c r="AB15" s="19">
         <f t="shared" si="12"/>
         <v>0.2121212121</v>
       </c>
-      <c r="AC15" s="24">
+      <c r="AC15" s="20">
         <f t="shared" si="6"/>
         <v>0.1726382175</v>
       </c>
-      <c r="AD15" s="12"/>
-      <c r="AE15" s="12"/>
+      <c r="AD15" s="11"/>
+      <c r="AE15" s="11"/>
       <c r="AF15" s="6">
         <v>1.758935803510798</v>
       </c>
@@ -1692,20 +1794,20 @@
         <f t="shared" si="7"/>
         <v>10.1885656</v>
       </c>
-      <c r="AH15" s="12"/>
-      <c r="AI15" s="12"/>
+      <c r="AH15" s="11"/>
+      <c r="AI15" s="11"/>
     </row>
     <row r="16">
-      <c r="B16" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>42</v>
+      <c r="B16" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>49</v>
       </c>
       <c r="D16" s="6">
         <v>6.0</v>
       </c>
-      <c r="E16" s="13">
+      <c r="E16" s="15">
         <f>155-31</f>
         <v>124</v>
       </c>
@@ -1724,8 +1826,8 @@
       <c r="J16" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="L16" s="9" t="s">
-        <v>24</v>
+      <c r="L16" s="10" t="s">
+        <v>28</v>
       </c>
       <c r="M16" s="17">
         <v>1.0</v>
@@ -1753,44 +1855,44 @@
       <c r="S16" s="17">
         <v>1.0</v>
       </c>
-      <c r="T16" s="12"/>
-      <c r="U16" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="V16" s="22">
+      <c r="T16" s="11"/>
+      <c r="U16" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="V16" s="19">
         <f t="shared" si="2"/>
         <v>0.04347826087</v>
       </c>
-      <c r="W16" s="22">
+      <c r="W16" s="19">
         <f t="shared" si="3"/>
         <v>0.04</v>
       </c>
-      <c r="X16" s="22">
+      <c r="X16" s="19">
         <f t="shared" si="4"/>
         <v>0.01157790275</v>
       </c>
-      <c r="Y16" s="22">
+      <c r="Y16" s="19">
         <f t="shared" ref="Y16:AB16" si="14">P16/P$17</f>
         <v>0.046854083</v>
       </c>
-      <c r="Z16" s="22">
+      <c r="Z16" s="19">
         <f t="shared" si="14"/>
         <v>0.00826446281</v>
       </c>
-      <c r="AA16" s="22">
+      <c r="AA16" s="19">
         <f t="shared" si="14"/>
         <v>0.008695652174</v>
       </c>
-      <c r="AB16" s="22">
+      <c r="AB16" s="19">
         <f t="shared" si="14"/>
         <v>0.0303030303</v>
       </c>
-      <c r="AC16" s="24">
+      <c r="AC16" s="20">
         <f t="shared" si="6"/>
         <v>0.02702477027</v>
       </c>
-      <c r="AD16" s="12"/>
-      <c r="AE16" s="12"/>
+      <c r="AD16" s="11"/>
+      <c r="AE16" s="11"/>
       <c r="AF16" s="6">
         <v>0.2892581518676131</v>
       </c>
@@ -1798,20 +1900,20 @@
         <f t="shared" si="7"/>
         <v>10.70344536</v>
       </c>
-      <c r="AH16" s="12"/>
-      <c r="AI16" s="12"/>
+      <c r="AH16" s="11"/>
+      <c r="AI16" s="11"/>
     </row>
     <row r="17">
-      <c r="B17" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>47</v>
+      <c r="B17" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>51</v>
       </c>
       <c r="D17" s="6">
         <v>6.0</v>
       </c>
-      <c r="E17" s="13">
+      <c r="E17" s="15">
         <f>220-67</f>
         <v>153</v>
       </c>
@@ -1830,8 +1932,8 @@
       <c r="J17" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="L17" s="11" t="s">
-        <v>59</v>
+      <c r="L17" s="7" t="s">
+        <v>63</v>
       </c>
       <c r="M17" s="26">
         <f t="shared" ref="M17:S17" si="15">SUM(M10:M16)</f>
@@ -1861,34 +1963,34 @@
         <f t="shared" si="15"/>
         <v>33</v>
       </c>
-      <c r="T17" s="12"/>
-      <c r="U17" s="12"/>
-      <c r="V17" s="12"/>
-      <c r="W17" s="12"/>
-      <c r="X17" s="12"/>
-      <c r="Y17" s="12"/>
-      <c r="Z17" s="12"/>
-      <c r="AA17" s="12"/>
-      <c r="AB17" s="12"/>
-      <c r="AC17" s="12"/>
-      <c r="AD17" s="12"/>
-      <c r="AE17" s="12"/>
-      <c r="AF17" s="29" t="s">
-        <v>59</v>
+      <c r="T17" s="11"/>
+      <c r="U17" s="11"/>
+      <c r="V17" s="11"/>
+      <c r="W17" s="11"/>
+      <c r="X17" s="11"/>
+      <c r="Y17" s="11"/>
+      <c r="Z17" s="11"/>
+      <c r="AA17" s="11"/>
+      <c r="AB17" s="11"/>
+      <c r="AC17" s="11"/>
+      <c r="AD17" s="11"/>
+      <c r="AE17" s="11"/>
+      <c r="AF17" s="28" t="s">
+        <v>63</v>
       </c>
       <c r="AG17" s="6">
         <f>SUM(AG10:AG16)</f>
         <v>87.18146576</v>
       </c>
-      <c r="AH17" s="12"/>
-      <c r="AI17" s="12"/>
+      <c r="AH17" s="11"/>
+      <c r="AI17" s="11"/>
     </row>
     <row r="18">
-      <c r="B18" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>49</v>
+      <c r="B18" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>53</v>
       </c>
       <c r="D18" s="6">
         <v>6.0</v>
@@ -1912,201 +2014,201 @@
       <c r="J18" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="L18" s="12"/>
-      <c r="M18" s="12"/>
-      <c r="N18" s="12"/>
-      <c r="O18" s="12"/>
-      <c r="P18" s="12"/>
-      <c r="Q18" s="12"/>
-      <c r="R18" s="12"/>
-      <c r="S18" s="12"/>
-      <c r="T18" s="12"/>
-      <c r="U18" s="12"/>
-      <c r="V18" s="12"/>
-      <c r="W18" s="12"/>
-      <c r="X18" s="12"/>
-      <c r="Y18" s="12"/>
-      <c r="Z18" s="12"/>
-      <c r="AA18" s="12"/>
-      <c r="AB18" s="12"/>
-      <c r="AC18" s="12"/>
-      <c r="AD18" s="12"/>
-      <c r="AE18" s="12"/>
-      <c r="AF18" s="29" t="s">
-        <v>63</v>
+      <c r="L18" s="11"/>
+      <c r="M18" s="11"/>
+      <c r="N18" s="11"/>
+      <c r="O18" s="11"/>
+      <c r="P18" s="11"/>
+      <c r="Q18" s="11"/>
+      <c r="R18" s="11"/>
+      <c r="S18" s="11"/>
+      <c r="T18" s="11"/>
+      <c r="U18" s="11"/>
+      <c r="V18" s="11"/>
+      <c r="W18" s="11"/>
+      <c r="X18" s="11"/>
+      <c r="Y18" s="11"/>
+      <c r="Z18" s="11"/>
+      <c r="AA18" s="11"/>
+      <c r="AB18" s="11"/>
+      <c r="AC18" s="11"/>
+      <c r="AD18" s="11"/>
+      <c r="AE18" s="11"/>
+      <c r="AF18" s="28" t="s">
+        <v>64</v>
       </c>
       <c r="AG18" s="6">
         <f>AG17/AE10</f>
         <v>12.45449511</v>
       </c>
-      <c r="AH18" s="12"/>
-      <c r="AI18" s="12"/>
+      <c r="AH18" s="11"/>
+      <c r="AI18" s="11"/>
     </row>
     <row r="19">
-      <c r="L19" s="31"/>
-      <c r="M19" s="31"/>
-      <c r="N19" s="31"/>
-      <c r="O19" s="31"/>
-      <c r="P19" s="31"/>
-      <c r="Q19" s="31"/>
-      <c r="R19" s="31"/>
-      <c r="S19" s="31"/>
-      <c r="T19" s="31"/>
-      <c r="U19" s="31"/>
-      <c r="V19" s="31"/>
-      <c r="W19" s="31"/>
-      <c r="X19" s="31"/>
-      <c r="Y19" s="31"/>
-      <c r="Z19" s="31"/>
-      <c r="AA19" s="31"/>
-      <c r="AB19" s="31"/>
-      <c r="AC19" s="31"/>
-      <c r="AD19" s="31"/>
-      <c r="AE19" s="31"/>
-      <c r="AF19" s="31"/>
-      <c r="AG19" s="12"/>
-      <c r="AH19" s="31"/>
-      <c r="AI19" s="31"/>
+      <c r="L19" s="29"/>
+      <c r="M19" s="29"/>
+      <c r="N19" s="29"/>
+      <c r="O19" s="29"/>
+      <c r="P19" s="29"/>
+      <c r="Q19" s="29"/>
+      <c r="R19" s="29"/>
+      <c r="S19" s="29"/>
+      <c r="T19" s="29"/>
+      <c r="U19" s="29"/>
+      <c r="V19" s="29"/>
+      <c r="W19" s="29"/>
+      <c r="X19" s="29"/>
+      <c r="Y19" s="29"/>
+      <c r="Z19" s="29"/>
+      <c r="AA19" s="29"/>
+      <c r="AB19" s="29"/>
+      <c r="AC19" s="29"/>
+      <c r="AD19" s="29"/>
+      <c r="AE19" s="29"/>
+      <c r="AF19" s="29"/>
+      <c r="AG19" s="11"/>
+      <c r="AH19" s="29"/>
+      <c r="AI19" s="29"/>
     </row>
     <row r="20">
-      <c r="L20" s="31"/>
-      <c r="M20" s="31"/>
-      <c r="N20" s="31"/>
-      <c r="O20" s="31"/>
-      <c r="P20" s="31"/>
-      <c r="Q20" s="31"/>
-      <c r="R20" s="31"/>
-      <c r="S20" s="31"/>
-      <c r="T20" s="31"/>
-      <c r="U20" s="31"/>
-      <c r="V20" s="31"/>
-      <c r="W20" s="31"/>
-      <c r="X20" s="31"/>
-      <c r="Y20" s="31"/>
-      <c r="Z20" s="31"/>
-      <c r="AA20" s="31"/>
-      <c r="AB20" s="31"/>
-      <c r="AC20" s="31"/>
-      <c r="AD20" s="31"/>
-      <c r="AE20" s="31"/>
-      <c r="AF20" s="33" t="s">
+      <c r="L20" s="29"/>
+      <c r="M20" s="29"/>
+      <c r="N20" s="29"/>
+      <c r="O20" s="29"/>
+      <c r="P20" s="29"/>
+      <c r="Q20" s="29"/>
+      <c r="R20" s="29"/>
+      <c r="S20" s="29"/>
+      <c r="T20" s="29"/>
+      <c r="U20" s="29"/>
+      <c r="V20" s="29"/>
+      <c r="W20" s="29"/>
+      <c r="X20" s="29"/>
+      <c r="Y20" s="29"/>
+      <c r="Z20" s="29"/>
+      <c r="AA20" s="29"/>
+      <c r="AB20" s="29"/>
+      <c r="AC20" s="29"/>
+      <c r="AD20" s="29"/>
+      <c r="AE20" s="29"/>
+      <c r="AF20" s="30" t="s">
         <v>65</v>
       </c>
-      <c r="AG20" s="13">
+      <c r="AG20" s="15">
         <f>(AG18-AE10)/(AE10-1)</f>
         <v>0.9090825182</v>
       </c>
-      <c r="AH20" s="31"/>
-      <c r="AI20" s="31"/>
+      <c r="AH20" s="29"/>
+      <c r="AI20" s="29"/>
     </row>
     <row r="21">
-      <c r="L21" s="31"/>
-      <c r="M21" s="31"/>
-      <c r="N21" s="31"/>
-      <c r="O21" s="31"/>
-      <c r="P21" s="31"/>
-      <c r="Q21" s="31"/>
-      <c r="R21" s="31"/>
-      <c r="S21" s="31"/>
-      <c r="T21" s="31"/>
-      <c r="U21" s="31"/>
-      <c r="V21" s="31"/>
-      <c r="W21" s="31"/>
-      <c r="X21" s="31"/>
-      <c r="Y21" s="31"/>
-      <c r="Z21" s="31"/>
-      <c r="AA21" s="31"/>
-      <c r="AB21" s="31"/>
-      <c r="AC21" s="31"/>
-      <c r="AD21" s="31"/>
-      <c r="AE21" s="31"/>
-      <c r="AF21" s="33" t="s">
+      <c r="L21" s="29"/>
+      <c r="M21" s="29"/>
+      <c r="N21" s="29"/>
+      <c r="O21" s="29"/>
+      <c r="P21" s="29"/>
+      <c r="Q21" s="29"/>
+      <c r="R21" s="29"/>
+      <c r="S21" s="29"/>
+      <c r="T21" s="29"/>
+      <c r="U21" s="29"/>
+      <c r="V21" s="29"/>
+      <c r="W21" s="29"/>
+      <c r="X21" s="29"/>
+      <c r="Y21" s="29"/>
+      <c r="Z21" s="29"/>
+      <c r="AA21" s="29"/>
+      <c r="AB21" s="29"/>
+      <c r="AC21" s="29"/>
+      <c r="AD21" s="29"/>
+      <c r="AE21" s="29"/>
+      <c r="AF21" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="AG21" s="23">
+        <v>1.32</v>
+      </c>
+      <c r="AH21" s="29"/>
+      <c r="AI21" s="29"/>
+    </row>
+    <row r="22">
+      <c r="AF22" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="AG21" s="21">
-        <v>1.32</v>
-      </c>
-      <c r="AH21" s="31"/>
-      <c r="AI21" s="31"/>
-    </row>
-    <row r="22">
-      <c r="AF22" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="AG22" s="19">
+      <c r="AG22" s="21">
         <f>AG20/AG21</f>
         <v>0.6886988774</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C24" s="5"/>
       <c r="D24" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="AF24" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="AF24" s="23" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="8"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G25" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="H25" s="10" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="7"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E25" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="G25" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H25" s="9" t="s">
+      <c r="I25" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J25" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="K25" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="I25" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="J25" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="K25" s="21" t="s">
-        <v>72</v>
-      </c>
     </row>
     <row r="26">
-      <c r="B26" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>27</v>
+      <c r="B26" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="D26" s="6">
         <v>18.0</v>
       </c>
-      <c r="E26" s="13">
+      <c r="E26" s="15">
         <f>75-17</f>
         <v>58</v>
       </c>
@@ -2127,16 +2229,16 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>30</v>
+      <c r="B27" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>39</v>
       </c>
       <c r="D27" s="6">
         <v>9.0</v>
       </c>
-      <c r="E27" s="13">
+      <c r="E27" s="15">
         <f>100-25</f>
         <v>75</v>
       </c>
@@ -2157,16 +2259,16 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>32</v>
+      <c r="B28" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>41</v>
       </c>
       <c r="D28" s="6">
         <v>6.0</v>
       </c>
-      <c r="E28" s="13">
+      <c r="E28" s="15">
         <f>180-30</f>
         <v>150</v>
       </c>
@@ -2187,16 +2289,16 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>34</v>
+      <c r="B29" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>43</v>
       </c>
       <c r="D29" s="6">
         <v>4.0</v>
       </c>
-      <c r="E29" s="13">
+      <c r="E29" s="15">
         <f>220-52</f>
         <v>168</v>
       </c>
@@ -2217,16 +2319,16 @@
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>37</v>
+      <c r="B30" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>45</v>
       </c>
       <c r="D30" s="6">
         <v>6.0</v>
       </c>
-      <c r="E30" s="13">
+      <c r="E30" s="15">
         <f>140 - 58</f>
         <v>82</v>
       </c>
@@ -2247,16 +2349,16 @@
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="C31" s="9" t="s">
-        <v>39</v>
+      <c r="B31" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>47</v>
       </c>
       <c r="D31" s="6">
         <v>6.0</v>
       </c>
-      <c r="E31" s="13">
+      <c r="E31" s="15">
         <f>140 - 54</f>
         <v>86</v>
       </c>
@@ -2277,16 +2379,16 @@
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>42</v>
+      <c r="B32" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>49</v>
       </c>
       <c r="D32" s="6">
         <v>6.0</v>
       </c>
-      <c r="E32" s="13">
+      <c r="E32" s="15">
         <f>155-31</f>
         <v>124</v>
       </c>
@@ -2307,16 +2409,16 @@
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C33" s="9" t="s">
-        <v>47</v>
+      <c r="B33" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>51</v>
       </c>
       <c r="D33" s="6">
         <v>6.0</v>
       </c>
-      <c r="E33" s="13">
+      <c r="E33" s="15">
         <f>220-67</f>
         <v>153</v>
       </c>
@@ -2337,11 +2439,11 @@
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>49</v>
+      <c r="B34" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>53</v>
       </c>
       <c r="D34" s="6">
         <v>6.0</v>
@@ -2366,8 +2468,8 @@
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="10" t="s">
-        <v>73</v>
+      <c r="B35" s="12" t="s">
+        <v>74</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>75</v>
@@ -2375,7 +2477,7 @@
       <c r="D35" s="6">
         <v>16.0</v>
       </c>
-      <c r="E35" s="13">
+      <c r="E35" s="15">
         <f>90-15</f>
         <v>75</v>
       </c>
@@ -2397,67 +2499,67 @@
     </row>
     <row r="40">
       <c r="B40" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C40" s="5"/>
       <c r="D40" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="7"/>
-      <c r="C41" s="8"/>
-      <c r="D41" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E41" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F41" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="G41" s="9" t="s">
+      <c r="B41" s="8"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="H41" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="I41" s="9" t="s">
+      <c r="E41" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F41" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="J41" s="9" t="s">
+      <c r="G41" s="10" t="s">
         <v>24</v>
       </c>
+      <c r="H41" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="I41" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J41" s="10" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="42">
-      <c r="B42" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C42" s="9" t="s">
-        <v>27</v>
+      <c r="B42" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="D42" s="6">
         <v>18.0</v>
       </c>
-      <c r="E42" s="13">
+      <c r="E42" s="15">
         <f>75-17</f>
         <v>58</v>
       </c>
@@ -2478,16 +2580,16 @@
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C43" s="9" t="s">
-        <v>30</v>
+      <c r="B43" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>39</v>
       </c>
       <c r="D43" s="6">
         <v>9.0</v>
       </c>
-      <c r="E43" s="13">
+      <c r="E43" s="15">
         <f>100-25</f>
         <v>75</v>
       </c>
@@ -2508,16 +2610,16 @@
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C44" s="9" t="s">
-        <v>32</v>
+      <c r="B44" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C44" s="10" t="s">
+        <v>41</v>
       </c>
       <c r="D44" s="6">
         <v>6.0</v>
       </c>
-      <c r="E44" s="13">
+      <c r="E44" s="15">
         <f>180-30</f>
         <v>150</v>
       </c>
@@ -2538,16 +2640,16 @@
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C45" s="9" t="s">
-        <v>34</v>
+      <c r="B45" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C45" s="10" t="s">
+        <v>43</v>
       </c>
       <c r="D45" s="6">
         <v>4.0</v>
       </c>
-      <c r="E45" s="13">
+      <c r="E45" s="15">
         <f>220-52</f>
         <v>168</v>
       </c>
@@ -2568,16 +2670,16 @@
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C46" s="9" t="s">
-        <v>37</v>
+      <c r="B46" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C46" s="10" t="s">
+        <v>45</v>
       </c>
       <c r="D46" s="6">
         <v>6.0</v>
       </c>
-      <c r="E46" s="13">
+      <c r="E46" s="15">
         <f>140 - 58</f>
         <v>82</v>
       </c>
@@ -2598,16 +2700,16 @@
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="C47" s="9" t="s">
-        <v>39</v>
+      <c r="B47" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C47" s="10" t="s">
+        <v>47</v>
       </c>
       <c r="D47" s="6">
         <v>6.0</v>
       </c>
-      <c r="E47" s="13">
+      <c r="E47" s="15">
         <f>140 - 54</f>
         <v>86</v>
       </c>
@@ -2628,16 +2730,16 @@
       </c>
     </row>
     <row r="48">
-      <c r="B48" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="C48" s="9" t="s">
-        <v>42</v>
+      <c r="B48" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C48" s="10" t="s">
+        <v>49</v>
       </c>
       <c r="D48" s="6">
         <v>6.0</v>
       </c>
-      <c r="E48" s="13">
+      <c r="E48" s="15">
         <f>155-31</f>
         <v>124</v>
       </c>
@@ -2658,16 +2760,16 @@
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C49" s="9" t="s">
-        <v>47</v>
+      <c r="B49" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C49" s="10" t="s">
+        <v>51</v>
       </c>
       <c r="D49" s="6">
         <v>6.0</v>
       </c>
-      <c r="E49" s="13">
+      <c r="E49" s="15">
         <f>220-67</f>
         <v>153</v>
       </c>
@@ -2688,11 +2790,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="B50" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="C50" s="9" t="s">
-        <v>49</v>
+      <c r="B50" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C50" s="10" t="s">
+        <v>53</v>
       </c>
       <c r="D50" s="6">
         <v>6.0</v>
@@ -2717,16 +2819,16 @@
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="10" t="s">
-        <v>73</v>
+      <c r="B51" s="12" t="s">
+        <v>74</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D51" s="6">
         <v>20.0</v>
       </c>
-      <c r="E51" s="13">
+      <c r="E51" s="15">
         <f>140 - 55</f>
         <v>85</v>
       </c>
@@ -2858,67 +2960,67 @@
     </row>
     <row r="8">
       <c r="B8" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="7"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="G9" s="9" t="s">
+      <c r="B9" s="8"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="E9" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="I9" s="9" t="s">
+      <c r="F9" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="J9" s="9" t="s">
+      <c r="G9" s="10" t="s">
         <v>24</v>
       </c>
+      <c r="H9" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J9" s="10" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="10">
-      <c r="B10" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>27</v>
+      <c r="B10" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="D10" s="6">
         <v>18.0</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="15">
         <f>75-17</f>
         <v>58</v>
       </c>
@@ -2939,16 +3041,16 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>30</v>
+      <c r="B11" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>39</v>
       </c>
       <c r="D11" s="6">
         <v>9.0</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="15">
         <f>100-25</f>
         <v>75</v>
       </c>
@@ -2969,16 +3071,16 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>32</v>
+      <c r="B12" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>41</v>
       </c>
       <c r="D12" s="6">
         <v>6.0</v>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="15">
         <f>180-30</f>
         <v>150</v>
       </c>
@@ -2999,16 +3101,16 @@
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>34</v>
+      <c r="B13" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>43</v>
       </c>
       <c r="D13" s="6">
         <v>4.0</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="15">
         <f>220-52</f>
         <v>168</v>
       </c>
@@ -3029,16 +3131,16 @@
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>37</v>
+      <c r="B14" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>45</v>
       </c>
       <c r="D14" s="6">
         <v>6.0</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="15">
         <f>140 - 58</f>
         <v>82</v>
       </c>
@@ -3059,16 +3161,16 @@
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>39</v>
+      <c r="B15" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>47</v>
       </c>
       <c r="D15" s="6">
         <v>6.0</v>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="15">
         <f>140 - 54</f>
         <v>86</v>
       </c>
@@ -3089,16 +3191,16 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>42</v>
+      <c r="B16" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>49</v>
       </c>
       <c r="D16" s="6">
         <v>6.0</v>
       </c>
-      <c r="E16" s="13">
+      <c r="E16" s="15">
         <f>155-31</f>
         <v>124</v>
       </c>
@@ -3119,16 +3221,16 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>47</v>
+      <c r="B17" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>51</v>
       </c>
       <c r="D17" s="6">
         <v>6.0</v>
       </c>
-      <c r="E17" s="13">
+      <c r="E17" s="15">
         <f>220-67</f>
         <v>153</v>
       </c>
@@ -3149,11 +3251,11 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>49</v>
+      <c r="B18" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>53</v>
       </c>
       <c r="D18" s="6">
         <v>6.0</v>
@@ -3180,138 +3282,138 @@
     </row>
     <row r="20">
       <c r="B20" s="4" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="M20" s="5"/>
       <c r="N20" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="Q20" s="6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="R20" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="S20" s="6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="T20" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="7"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="G21" s="9" t="s">
+      <c r="B21" s="8"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="H21" s="9" t="s">
+      <c r="E21" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="I21" s="9" t="s">
+      <c r="F21" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="J21" s="9" t="s">
+      <c r="G21" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="L21" s="7"/>
-      <c r="M21" s="8"/>
-      <c r="N21" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="O21" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="P21" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q21" s="9" t="s">
+      <c r="H21" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="I21" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J21" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="L21" s="8"/>
+      <c r="M21" s="9"/>
+      <c r="N21" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="R21" s="9" t="s">
+      <c r="O21" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="S21" s="9" t="s">
+      <c r="P21" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="T21" s="9" t="s">
+      <c r="Q21" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="W21" s="19"/>
-      <c r="X21" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="Y21" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z21" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="AA21" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="AB21" s="20" t="s">
+      <c r="R21" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="S21" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="T21" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="W21" s="21"/>
+      <c r="X21" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="AC21" s="20" t="s">
+      <c r="Y21" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="AD21" s="20" t="s">
+      <c r="Z21" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="AG21" s="21"/>
+      <c r="AA21" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="AB21" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="AC21" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD21" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="AG21" s="23"/>
     </row>
     <row r="22">
-      <c r="B22" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>27</v>
+      <c r="B22" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="D22" s="6">
         <v>18.0</v>
       </c>
-      <c r="E22" s="13">
+      <c r="E22" s="15">
         <f>75-17</f>
         <v>58</v>
       </c>
@@ -3330,17 +3432,17 @@
       <c r="J22" s="6">
         <v>5.0</v>
       </c>
-      <c r="L22" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="M22" s="9" t="s">
-        <v>27</v>
+      <c r="L22" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="M22" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="N22" s="6">
         <f t="shared" ref="N22:N30" si="2">(D22-$D$32)/$D$33</f>
         <v>1</v>
       </c>
-      <c r="O22" s="13">
+      <c r="O22" s="15">
         <f t="shared" ref="O22:O30" si="3">(E22-$E$32)/$E$33</f>
         <v>0</v>
       </c>
@@ -3360,16 +3462,16 @@
         <f t="shared" ref="S22:S30" si="7">($I$31-I22)/$I$33</f>
         <v>0</v>
       </c>
-      <c r="T22" s="23">
+      <c r="T22" s="24">
         <f t="shared" ref="T22:T30" si="8">(J22-$J$32)/$J$33</f>
         <v>1</v>
       </c>
-      <c r="U22" s="19">
+      <c r="U22" s="21">
         <f t="shared" ref="U22:U30" si="9">SUMPRODUCT(N22:T22,$X$41:$AD$41)</f>
         <v>0.492000777</v>
       </c>
-      <c r="W22" s="20" t="s">
-        <v>52</v>
+      <c r="W22" s="22" t="s">
+        <v>56</v>
       </c>
       <c r="X22" s="25">
         <f>CORREL(N22:N30,N22:N30)</f>
@@ -3401,16 +3503,16 @@
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>30</v>
+      <c r="B23" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>39</v>
       </c>
       <c r="D23" s="6">
         <v>9.0</v>
       </c>
-      <c r="E23" s="13">
+      <c r="E23" s="15">
         <f>100-25</f>
         <v>75</v>
       </c>
@@ -3429,17 +3531,17 @@
       <c r="J23" s="6">
         <v>5.0</v>
       </c>
-      <c r="L23" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="M23" s="9" t="s">
-        <v>30</v>
+      <c r="L23" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M23" s="10" t="s">
+        <v>39</v>
       </c>
       <c r="N23" s="6">
         <f t="shared" si="2"/>
         <v>0.3571428571</v>
       </c>
-      <c r="O23" s="13">
+      <c r="O23" s="15">
         <f t="shared" si="3"/>
         <v>0.1531531532</v>
       </c>
@@ -3459,16 +3561,16 @@
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="T23" s="23">
+      <c r="T23" s="24">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="U23" s="19">
+      <c r="U23" s="21">
         <f t="shared" si="9"/>
         <v>0.4960689324</v>
       </c>
-      <c r="W23" s="20" t="s">
-        <v>53</v>
+      <c r="W23" s="22" t="s">
+        <v>57</v>
       </c>
       <c r="X23" s="25">
         <f t="shared" ref="X23:AD23" si="10">CORREL(N22:N30,$O$22:$O$30)</f>
@@ -3500,16 +3602,16 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>32</v>
+      <c r="B24" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>41</v>
       </c>
       <c r="D24" s="6">
         <v>6.0</v>
       </c>
-      <c r="E24" s="13">
+      <c r="E24" s="15">
         <f>180-30</f>
         <v>150</v>
       </c>
@@ -3528,17 +3630,17 @@
       <c r="J24" s="6">
         <v>3.0</v>
       </c>
-      <c r="L24" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="M24" s="9" t="s">
-        <v>32</v>
+      <c r="L24" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="M24" s="10" t="s">
+        <v>41</v>
       </c>
       <c r="N24" s="6">
         <f t="shared" si="2"/>
         <v>0.1428571429</v>
       </c>
-      <c r="O24" s="13">
+      <c r="O24" s="15">
         <f t="shared" si="3"/>
         <v>0.8288288288</v>
       </c>
@@ -3558,16 +3660,16 @@
         <f t="shared" si="7"/>
         <v>0.7142857143</v>
       </c>
-      <c r="T24" s="23">
+      <c r="T24" s="24">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="U24" s="19">
+      <c r="U24" s="21">
         <f t="shared" si="9"/>
         <v>0.4240747446</v>
       </c>
-      <c r="W24" s="20" t="s">
-        <v>54</v>
+      <c r="W24" s="22" t="s">
+        <v>58</v>
       </c>
       <c r="X24" s="25">
         <f t="shared" ref="X24:AD24" si="11">CORREL($P$22:$P$30,N22:N30)</f>
@@ -3599,16 +3701,16 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>34</v>
+      <c r="B25" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>43</v>
       </c>
       <c r="D25" s="6">
         <v>4.0</v>
       </c>
-      <c r="E25" s="13">
+      <c r="E25" s="15">
         <f>220-52</f>
         <v>168</v>
       </c>
@@ -3627,17 +3729,17 @@
       <c r="J25" s="6">
         <v>4.0</v>
       </c>
-      <c r="L25" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="M25" s="9" t="s">
-        <v>34</v>
+      <c r="L25" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="M25" s="10" t="s">
+        <v>43</v>
       </c>
       <c r="N25" s="6">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O25" s="13">
+      <c r="O25" s="15">
         <f t="shared" si="3"/>
         <v>0.990990991</v>
       </c>
@@ -3657,16 +3759,16 @@
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="T25" s="23">
+      <c r="T25" s="24">
         <f t="shared" si="8"/>
         <v>0.5</v>
       </c>
-      <c r="U25" s="19">
+      <c r="U25" s="21">
         <f t="shared" si="9"/>
         <v>0.652462462</v>
       </c>
-      <c r="W25" s="20" t="s">
-        <v>55</v>
+      <c r="W25" s="22" t="s">
+        <v>59</v>
       </c>
       <c r="X25" s="25">
         <f t="shared" ref="X25:AD25" si="12">CORREL(N22:N30,$Q$22:$Q$30)</f>
@@ -3698,16 +3800,16 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>37</v>
+      <c r="B26" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>45</v>
       </c>
       <c r="D26" s="6">
         <v>6.0</v>
       </c>
-      <c r="E26" s="13">
+      <c r="E26" s="15">
         <f>140 - 58</f>
         <v>82</v>
       </c>
@@ -3726,17 +3828,17 @@
       <c r="J26" s="6">
         <v>4.0</v>
       </c>
-      <c r="L26" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="M26" s="9" t="s">
-        <v>37</v>
+      <c r="L26" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="M26" s="10" t="s">
+        <v>45</v>
       </c>
       <c r="N26" s="6">
         <f t="shared" si="2"/>
         <v>0.1428571429</v>
       </c>
-      <c r="O26" s="13">
+      <c r="O26" s="15">
         <f t="shared" si="3"/>
         <v>0.2162162162</v>
       </c>
@@ -3756,16 +3858,16 @@
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="T26" s="23">
+      <c r="T26" s="24">
         <f t="shared" si="8"/>
         <v>0.5</v>
       </c>
-      <c r="U26" s="19">
+      <c r="U26" s="21">
         <f t="shared" si="9"/>
         <v>0.524969644</v>
       </c>
-      <c r="W26" s="20" t="s">
-        <v>56</v>
+      <c r="W26" s="22" t="s">
+        <v>60</v>
       </c>
       <c r="X26" s="25">
         <f t="shared" ref="X26:AD26" si="13">CORREL(N22:N30,$R$22:$R$30)</f>
@@ -3797,16 +3899,16 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>39</v>
+      <c r="B27" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>47</v>
       </c>
       <c r="D27" s="6">
         <v>6.0</v>
       </c>
-      <c r="E27" s="13">
+      <c r="E27" s="15">
         <f>140 - 54</f>
         <v>86</v>
       </c>
@@ -3825,17 +3927,17 @@
       <c r="J27" s="6">
         <v>4.0</v>
       </c>
-      <c r="L27" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="M27" s="9" t="s">
-        <v>39</v>
+      <c r="L27" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="M27" s="10" t="s">
+        <v>47</v>
       </c>
       <c r="N27" s="6">
         <f t="shared" si="2"/>
         <v>0.1428571429</v>
       </c>
-      <c r="O27" s="13">
+      <c r="O27" s="15">
         <f t="shared" si="3"/>
         <v>0.2522522523</v>
       </c>
@@ -3855,16 +3957,16 @@
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="T27" s="23">
+      <c r="T27" s="24">
         <f t="shared" si="8"/>
         <v>0.5</v>
       </c>
-      <c r="U27" s="19">
+      <c r="U27" s="21">
         <f t="shared" si="9"/>
         <v>0.5315359773</v>
       </c>
-      <c r="W27" s="20" t="s">
-        <v>57</v>
+      <c r="W27" s="22" t="s">
+        <v>61</v>
       </c>
       <c r="X27" s="25">
         <f t="shared" ref="X27:AD27" si="14">CORREL($S$22:$S$30,N22:N30)</f>
@@ -3896,16 +3998,16 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>42</v>
+      <c r="B28" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>49</v>
       </c>
       <c r="D28" s="6">
         <v>6.0</v>
       </c>
-      <c r="E28" s="13">
+      <c r="E28" s="15">
         <f>155-31</f>
         <v>124</v>
       </c>
@@ -3924,17 +4026,17 @@
       <c r="J28" s="6">
         <v>5.0</v>
       </c>
-      <c r="L28" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="M28" s="9" t="s">
-        <v>42</v>
+      <c r="L28" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="M28" s="10" t="s">
+        <v>49</v>
       </c>
       <c r="N28" s="6">
         <f t="shared" si="2"/>
         <v>0.1428571429</v>
       </c>
-      <c r="O28" s="13">
+      <c r="O28" s="15">
         <f t="shared" si="3"/>
         <v>0.5945945946</v>
       </c>
@@ -3954,16 +4056,16 @@
         <f t="shared" si="7"/>
         <v>0.8571428571</v>
       </c>
-      <c r="T28" s="23">
+      <c r="T28" s="24">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="U28" s="19">
+      <c r="U28" s="21">
         <f t="shared" si="9"/>
         <v>0.6966864369</v>
       </c>
-      <c r="W28" s="20" t="s">
-        <v>58</v>
+      <c r="W28" s="22" t="s">
+        <v>62</v>
       </c>
       <c r="X28" s="25">
         <f t="shared" ref="X28:AD28" si="15">CORREL($T$22:$T$30,N22:N30)</f>
@@ -3995,16 +4097,16 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>47</v>
+      <c r="B29" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>51</v>
       </c>
       <c r="D29" s="6">
         <v>6.0</v>
       </c>
-      <c r="E29" s="13">
+      <c r="E29" s="15">
         <f>220-67</f>
         <v>153</v>
       </c>
@@ -4023,17 +4125,17 @@
       <c r="J29" s="6">
         <v>4.0</v>
       </c>
-      <c r="L29" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="M29" s="9" t="s">
-        <v>47</v>
+      <c r="L29" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="M29" s="10" t="s">
+        <v>51</v>
       </c>
       <c r="N29" s="6">
         <f t="shared" si="2"/>
         <v>0.1428571429</v>
       </c>
-      <c r="O29" s="13">
+      <c r="O29" s="15">
         <f t="shared" si="3"/>
         <v>0.8558558559</v>
       </c>
@@ -4053,21 +4155,21 @@
         <f t="shared" si="7"/>
         <v>0.7142857143</v>
       </c>
-      <c r="T29" s="23">
+      <c r="T29" s="24">
         <f t="shared" si="8"/>
         <v>0.5</v>
       </c>
-      <c r="U29" s="19">
+      <c r="U29" s="21">
         <f t="shared" si="9"/>
         <v>0.5639380603</v>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>49</v>
+      <c r="B30" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>53</v>
       </c>
       <c r="D30" s="6">
         <v>6.0</v>
@@ -4091,17 +4193,17 @@
       <c r="J30" s="6">
         <v>4.0</v>
       </c>
-      <c r="L30" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="M30" s="9" t="s">
-        <v>49</v>
+      <c r="L30" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="M30" s="10" t="s">
+        <v>53</v>
       </c>
       <c r="N30" s="6">
         <f t="shared" si="2"/>
         <v>0.1428571429</v>
       </c>
-      <c r="O30" s="13">
+      <c r="O30" s="15">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -4121,172 +4223,172 @@
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="T30" s="23">
+      <c r="T30" s="24">
         <f t="shared" si="8"/>
         <v>0.5</v>
       </c>
-      <c r="U30" s="19">
+      <c r="U30" s="21">
         <f t="shared" si="9"/>
         <v>0.4526568561</v>
       </c>
-      <c r="W30" s="21" t="s">
-        <v>60</v>
+      <c r="W30" s="23" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="31">
-      <c r="C31" s="28" t="s">
-        <v>61</v>
-      </c>
-      <c r="D31" s="30">
+      <c r="C31" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="D31" s="32">
         <f t="shared" ref="D31:J31" si="16">MAX(D22:D30)</f>
         <v>18</v>
       </c>
-      <c r="E31" s="30">
+      <c r="E31" s="32">
         <f t="shared" si="16"/>
         <v>169</v>
       </c>
-      <c r="F31" s="30">
+      <c r="F31" s="32">
         <f t="shared" si="16"/>
         <v>90</v>
       </c>
-      <c r="G31" s="30">
+      <c r="G31" s="32">
         <f t="shared" si="16"/>
         <v>4</v>
       </c>
-      <c r="H31" s="30">
+      <c r="H31" s="32">
         <f t="shared" si="16"/>
         <v>14</v>
       </c>
-      <c r="I31" s="30">
+      <c r="I31" s="32">
         <f t="shared" si="16"/>
         <v>7</v>
       </c>
-      <c r="J31" s="30">
+      <c r="J31" s="32">
         <f t="shared" si="16"/>
         <v>5</v>
       </c>
-      <c r="M31" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="N31" s="19">
+      <c r="M31" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="N31" s="21">
         <f t="shared" ref="N31:T31" si="17">STDEV(N22:N30)</f>
         <v>0.2969039027</v>
       </c>
-      <c r="O31" s="19">
+      <c r="O31" s="21">
         <f t="shared" si="17"/>
         <v>0.3920989409</v>
       </c>
-      <c r="P31" s="19">
+      <c r="P31" s="21">
         <f t="shared" si="17"/>
         <v>0.3574709692</v>
       </c>
-      <c r="Q31" s="19">
+      <c r="Q31" s="21">
         <f t="shared" si="17"/>
         <v>0.3643021402</v>
       </c>
-      <c r="R31" s="19">
+      <c r="R31" s="21">
         <f t="shared" si="17"/>
         <v>0.3974746673</v>
       </c>
-      <c r="S31" s="19">
+      <c r="S31" s="21">
         <f t="shared" si="17"/>
         <v>0.3273268354</v>
       </c>
-      <c r="T31" s="19">
+      <c r="T31" s="21">
         <f t="shared" si="17"/>
         <v>0.3333333333</v>
       </c>
-      <c r="U31" s="32"/>
+      <c r="U31" s="33"/>
     </row>
     <row r="32">
-      <c r="C32" s="28" t="s">
-        <v>64</v>
-      </c>
-      <c r="D32" s="30">
+      <c r="C32" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="D32" s="32">
         <f t="shared" ref="D32:J32" si="18">MIN(D22:D30)</f>
         <v>4</v>
       </c>
-      <c r="E32" s="30">
+      <c r="E32" s="32">
         <f t="shared" si="18"/>
         <v>58</v>
       </c>
-      <c r="F32" s="30">
+      <c r="F32" s="32">
         <f t="shared" si="18"/>
         <v>30</v>
       </c>
-      <c r="G32" s="30">
+      <c r="G32" s="32">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
-      <c r="H32" s="30">
+      <c r="H32" s="32">
         <f t="shared" si="18"/>
         <v>2</v>
       </c>
-      <c r="I32" s="30">
+      <c r="I32" s="32">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="J32" s="30">
+      <c r="J32" s="32">
         <f t="shared" si="18"/>
         <v>3</v>
       </c>
-      <c r="W32" s="10"/>
-      <c r="X32" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="Y32" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z32" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="AA32" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="AB32" s="20" t="s">
+      <c r="W32" s="12"/>
+      <c r="X32" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="AC32" s="20" t="s">
+      <c r="Y32" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="AD32" s="20" t="s">
+      <c r="Z32" s="22" t="s">
         <v>58</v>
       </c>
+      <c r="AA32" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="AB32" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="AC32" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD32" s="22" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="33">
-      <c r="C33" s="28" t="s">
-        <v>66</v>
-      </c>
-      <c r="D33" s="30">
+      <c r="C33" s="31" t="s">
+        <v>79</v>
+      </c>
+      <c r="D33" s="32">
         <f t="shared" ref="D33:J33" si="19">D31-D32</f>
         <v>14</v>
       </c>
-      <c r="E33" s="30">
+      <c r="E33" s="32">
         <f t="shared" si="19"/>
         <v>111</v>
       </c>
-      <c r="F33" s="30">
+      <c r="F33" s="32">
         <f t="shared" si="19"/>
         <v>60</v>
       </c>
-      <c r="G33" s="30">
+      <c r="G33" s="32">
         <f t="shared" si="19"/>
         <v>3</v>
       </c>
-      <c r="H33" s="30">
+      <c r="H33" s="32">
         <f t="shared" si="19"/>
         <v>12</v>
       </c>
-      <c r="I33" s="30">
+      <c r="I33" s="32">
         <f t="shared" si="19"/>
         <v>7</v>
       </c>
-      <c r="J33" s="30">
+      <c r="J33" s="32">
         <f t="shared" si="19"/>
         <v>2</v>
       </c>
-      <c r="W33" s="20" t="s">
-        <v>52</v>
+      <c r="W33" s="22" t="s">
+        <v>56</v>
       </c>
       <c r="X33" s="34">
         <f t="shared" ref="X33:AD33" si="20">1-X22</f>
@@ -4318,8 +4420,8 @@
       </c>
     </row>
     <row r="34">
-      <c r="W34" s="20" t="s">
-        <v>53</v>
+      <c r="W34" s="22" t="s">
+        <v>57</v>
       </c>
       <c r="X34" s="34">
         <f t="shared" ref="X34:AD34" si="21">1-X23</f>
@@ -4351,8 +4453,8 @@
       </c>
     </row>
     <row r="35">
-      <c r="W35" s="20" t="s">
-        <v>54</v>
+      <c r="W35" s="22" t="s">
+        <v>58</v>
       </c>
       <c r="X35" s="34">
         <f t="shared" ref="X35:AD35" si="22">1-X24</f>
@@ -4384,8 +4486,8 @@
       </c>
     </row>
     <row r="36">
-      <c r="W36" s="20" t="s">
-        <v>55</v>
+      <c r="W36" s="22" t="s">
+        <v>59</v>
       </c>
       <c r="X36" s="34">
         <f t="shared" ref="X36:AD36" si="23">1-X25</f>
@@ -4417,8 +4519,8 @@
       </c>
     </row>
     <row r="37">
-      <c r="W37" s="20" t="s">
-        <v>56</v>
+      <c r="W37" s="22" t="s">
+        <v>60</v>
       </c>
       <c r="X37" s="34">
         <f t="shared" ref="X37:AD37" si="24">1-X26</f>
@@ -4450,8 +4552,8 @@
       </c>
     </row>
     <row r="38">
-      <c r="W38" s="20" t="s">
-        <v>57</v>
+      <c r="W38" s="22" t="s">
+        <v>61</v>
       </c>
       <c r="X38" s="34">
         <f t="shared" ref="X38:AD38" si="25">1-X27</f>
@@ -4483,8 +4585,8 @@
       </c>
     </row>
     <row r="39">
-      <c r="W39" s="20" t="s">
-        <v>58</v>
+      <c r="W39" s="22" t="s">
+        <v>62</v>
       </c>
       <c r="X39" s="34">
         <f t="shared" ref="X39:AD39" si="26">1-X28</f>
@@ -4516,67 +4618,67 @@
       </c>
     </row>
     <row r="40">
-      <c r="W40" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="X40" s="35">
+      <c r="W40" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="X40" s="38">
         <f t="shared" ref="X40:AD40" si="27">N31*SUM(X33:X39)</f>
         <v>1.971752515</v>
       </c>
-      <c r="Y40" s="35">
+      <c r="Y40" s="38">
         <f t="shared" si="27"/>
         <v>2.906329297</v>
       </c>
-      <c r="Z40" s="35">
+      <c r="Z40" s="38">
         <f t="shared" si="27"/>
         <v>1.989777066</v>
       </c>
-      <c r="AA40" s="35">
+      <c r="AA40" s="38">
         <f t="shared" si="27"/>
         <v>2.035514555</v>
       </c>
-      <c r="AB40" s="35">
+      <c r="AB40" s="38">
         <f t="shared" si="27"/>
         <v>2.786072198</v>
       </c>
-      <c r="AC40" s="35">
+      <c r="AC40" s="38">
         <f t="shared" si="27"/>
         <v>2.410152965</v>
       </c>
-      <c r="AD40" s="35">
+      <c r="AD40" s="38">
         <f t="shared" si="27"/>
         <v>1.850336155</v>
       </c>
     </row>
     <row r="41">
-      <c r="W41" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="X41" s="35">
+      <c r="W41" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="X41" s="38">
         <f t="shared" ref="X41:AD41" si="28">X40/SUM($X$40:$AD$40)</f>
         <v>0.123621353</v>
       </c>
-      <c r="Y41" s="35">
+      <c r="Y41" s="38">
         <f t="shared" si="28"/>
         <v>0.1822157484</v>
       </c>
-      <c r="Z41" s="35">
+      <c r="Z41" s="38">
         <f t="shared" si="28"/>
         <v>0.1247514236</v>
       </c>
-      <c r="AA41" s="35">
+      <c r="AA41" s="38">
         <f t="shared" si="28"/>
         <v>0.1276189895</v>
       </c>
-      <c r="AB41" s="35">
+      <c r="AB41" s="38">
         <f t="shared" si="28"/>
         <v>0.1746760875</v>
       </c>
-      <c r="AC41" s="35">
+      <c r="AC41" s="38">
         <f t="shared" si="28"/>
         <v>0.1511073871</v>
       </c>
-      <c r="AD41" s="35">
+      <c r="AD41" s="38">
         <f t="shared" si="28"/>
         <v>0.1160090109</v>
       </c>
@@ -4591,4 +4693,2007 @@
   </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="34" max="34" width="14.13"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="3"/>
+      <c r="C3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E3" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="F3" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="G3" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="H3" s="2">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="3"/>
+      <c r="C6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E6" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="F6" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="G6" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="H6" s="2">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="5"/>
+      <c r="D8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M8" s="5"/>
+      <c r="N8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="O8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="P8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="S8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="T8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="V8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="W8" s="5"/>
+      <c r="X8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="AE8" s="11"/>
+      <c r="AF8" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG8" s="5"/>
+      <c r="AH8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="AI8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="AJ8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="AK8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="AL8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="AM8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="AN8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="AO8" s="11"/>
+      <c r="AP8" s="11"/>
+      <c r="AQ8" s="11"/>
+      <c r="AR8" s="11"/>
+      <c r="AS8" s="11"/>
+      <c r="AT8" s="11"/>
+      <c r="AU8" s="11"/>
+      <c r="AV8" s="11"/>
+      <c r="AW8" s="11"/>
+      <c r="AX8" s="11"/>
+      <c r="AY8" s="11"/>
+      <c r="AZ8" s="11"/>
+      <c r="BA8" s="11"/>
+      <c r="BB8" s="11"/>
+      <c r="BC8" s="11"/>
+      <c r="BD8" s="11"/>
+      <c r="BE8" s="11"/>
+      <c r="BF8" s="11"/>
+      <c r="BG8" s="11"/>
+      <c r="BH8" s="11"/>
+      <c r="BI8" s="11"/>
+      <c r="BJ8" s="11"/>
+      <c r="BK8" s="11"/>
+      <c r="BL8" s="11"/>
+      <c r="BM8" s="11"/>
+      <c r="BN8" s="11"/>
+      <c r="BO8" s="11"/>
+      <c r="BP8" s="11"/>
+      <c r="BQ8" s="11"/>
+      <c r="BR8" s="11"/>
+      <c r="BS8" s="11"/>
+      <c r="BT8" s="11"/>
+      <c r="BU8" s="11"/>
+    </row>
+    <row r="9">
+      <c r="B9" s="8"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J9" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="L9" s="8"/>
+      <c r="M9" s="9"/>
+      <c r="N9" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="O9" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="P9" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q9" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="R9" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="S9" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="T9" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="V9" s="8"/>
+      <c r="W9" s="9"/>
+      <c r="X9" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y9" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z9" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA9" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB9" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC9" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD9" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE9" s="14"/>
+      <c r="AF9" s="8"/>
+      <c r="AG9" s="9"/>
+      <c r="AH9" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI9" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="AJ9" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="AK9" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="AL9" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM9" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="AN9" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="AO9" s="14"/>
+      <c r="AP9" s="14"/>
+      <c r="AQ9" s="14"/>
+      <c r="AR9" s="14"/>
+      <c r="AS9" s="14"/>
+      <c r="AT9" s="14"/>
+      <c r="AU9" s="14"/>
+      <c r="AV9" s="14"/>
+      <c r="AW9" s="14"/>
+      <c r="AX9" s="14"/>
+      <c r="AY9" s="14"/>
+      <c r="AZ9" s="14"/>
+      <c r="BA9" s="14"/>
+      <c r="BB9" s="14"/>
+      <c r="BC9" s="14"/>
+      <c r="BD9" s="14"/>
+      <c r="BE9" s="14"/>
+      <c r="BF9" s="14"/>
+      <c r="BG9" s="14"/>
+      <c r="BH9" s="14"/>
+      <c r="BI9" s="14"/>
+      <c r="BJ9" s="14"/>
+      <c r="BK9" s="14"/>
+      <c r="BL9" s="14"/>
+      <c r="BM9" s="14"/>
+      <c r="BN9" s="14"/>
+      <c r="BO9" s="14"/>
+      <c r="BP9" s="14"/>
+      <c r="BQ9" s="14"/>
+      <c r="BR9" s="14"/>
+      <c r="BS9" s="14"/>
+      <c r="BT9" s="14"/>
+      <c r="BU9" s="14"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" s="6">
+        <v>18.0</v>
+      </c>
+      <c r="E10" s="15">
+        <f>75-17</f>
+        <v>58</v>
+      </c>
+      <c r="F10" s="6">
+        <v>30.0</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="H10" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="I10" s="6">
+        <v>7.0</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="L10" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="M10" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="N10" s="6">
+        <v>18.0</v>
+      </c>
+      <c r="O10" s="15">
+        <f>75-17</f>
+        <v>58</v>
+      </c>
+      <c r="P10" s="6">
+        <f t="shared" ref="P10:P18" si="2">1/F10</f>
+        <v>0.03333333333</v>
+      </c>
+      <c r="Q10" s="6">
+        <f>1/D3</f>
+        <v>1</v>
+      </c>
+      <c r="R10" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="S10" s="6">
+        <f>1/I10</f>
+        <v>0.1428571429</v>
+      </c>
+      <c r="T10" s="6">
+        <f t="shared" ref="T10:T11" si="3">1/$H$6</f>
+        <v>0.2</v>
+      </c>
+      <c r="V10" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="W10" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="X10" s="6">
+        <f t="shared" ref="X10:X18" si="4">N10/$N$19</f>
+        <v>0.2686567164</v>
+      </c>
+      <c r="Y10" s="15">
+        <f t="shared" ref="Y10:Y18" si="5">O10/$O$19</f>
+        <v>0.0544600939</v>
+      </c>
+      <c r="Z10" s="6">
+        <f t="shared" ref="Z10:Z18" si="6">P10/$P$19</f>
+        <v>0.1706942004</v>
+      </c>
+      <c r="AA10" s="6">
+        <f t="shared" ref="AA10:AA18" si="7">Q10/$Q$19</f>
+        <v>0.1904761905</v>
+      </c>
+      <c r="AB10" s="6">
+        <f t="shared" ref="AB10:AB18" si="8">R10/$R$19</f>
+        <v>0.0350877193</v>
+      </c>
+      <c r="AC10" s="6">
+        <f t="shared" ref="AC10:AC18" si="9">S10/$S$19</f>
+        <v>0.06666666667</v>
+      </c>
+      <c r="AD10" s="6">
+        <f t="shared" ref="AD10:AD18" si="10">T10/$T$19</f>
+        <v>0.09160305344</v>
+      </c>
+      <c r="AE10" s="11"/>
+      <c r="AF10" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="AG10" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH10" s="20">
+        <f t="shared" ref="AH10:AL10" si="1">LN(X10)</f>
+        <v>-1.314320861</v>
+      </c>
+      <c r="AI10" s="20">
+        <f t="shared" si="1"/>
+        <v>-2.910287068</v>
+      </c>
+      <c r="AJ10" s="20">
+        <f t="shared" si="1"/>
+        <v>-1.767881625</v>
+      </c>
+      <c r="AK10" s="20">
+        <f t="shared" si="1"/>
+        <v>-1.658228077</v>
+      </c>
+      <c r="AL10" s="20">
+        <f t="shared" si="1"/>
+        <v>-3.349904087</v>
+      </c>
+      <c r="AM10" s="20">
+        <f t="shared" ref="AM10:AM18" si="12">IF(AC10 = 0, 0, Ln(AC10))</f>
+        <v>-2.708050201</v>
+      </c>
+      <c r="AN10" s="20">
+        <f t="shared" ref="AN10:AN18" si="13">LN(AD10)</f>
+        <v>-2.390290673</v>
+      </c>
+      <c r="AO10" s="11"/>
+      <c r="AP10" s="11"/>
+      <c r="AQ10" s="11"/>
+      <c r="AR10" s="11"/>
+      <c r="AS10" s="11"/>
+      <c r="AT10" s="11"/>
+      <c r="AU10" s="11"/>
+      <c r="AV10" s="11"/>
+      <c r="AW10" s="11"/>
+      <c r="AX10" s="11"/>
+      <c r="AY10" s="11"/>
+      <c r="AZ10" s="11"/>
+      <c r="BA10" s="11"/>
+      <c r="BB10" s="11"/>
+      <c r="BC10" s="11"/>
+      <c r="BD10" s="11"/>
+      <c r="BE10" s="11"/>
+      <c r="BF10" s="11"/>
+      <c r="BG10" s="11"/>
+      <c r="BH10" s="11"/>
+      <c r="BI10" s="11"/>
+      <c r="BJ10" s="11"/>
+      <c r="BK10" s="11"/>
+      <c r="BL10" s="11"/>
+      <c r="BM10" s="11"/>
+      <c r="BN10" s="11"/>
+      <c r="BO10" s="11"/>
+      <c r="BP10" s="11"/>
+      <c r="BQ10" s="11"/>
+      <c r="BR10" s="11"/>
+      <c r="BS10" s="11"/>
+      <c r="BT10" s="11"/>
+      <c r="BU10" s="11"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="6">
+        <v>9.0</v>
+      </c>
+      <c r="E11" s="15">
+        <f>100-25</f>
+        <v>75</v>
+      </c>
+      <c r="F11" s="6">
+        <v>35.0</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H11" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="I11" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="L11" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M11" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="N11" s="6">
+        <v>9.0</v>
+      </c>
+      <c r="O11" s="15">
+        <f>100-25</f>
+        <v>75</v>
+      </c>
+      <c r="P11" s="6">
+        <f t="shared" si="2"/>
+        <v>0.02857142857</v>
+      </c>
+      <c r="Q11" s="6">
+        <f>1/F3</f>
+        <v>0.3333333333</v>
+      </c>
+      <c r="R11" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="S11" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="T11" s="6">
+        <f t="shared" si="3"/>
+        <v>0.2</v>
+      </c>
+      <c r="V11" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="W11" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="X11" s="6">
+        <f t="shared" si="4"/>
+        <v>0.1343283582</v>
+      </c>
+      <c r="Y11" s="15">
+        <f t="shared" si="5"/>
+        <v>0.07042253521</v>
+      </c>
+      <c r="Z11" s="6">
+        <f t="shared" si="6"/>
+        <v>0.1463093146</v>
+      </c>
+      <c r="AA11" s="6">
+        <f t="shared" si="7"/>
+        <v>0.06349206349</v>
+      </c>
+      <c r="AB11" s="6">
+        <f t="shared" si="8"/>
+        <v>0.0350877193</v>
+      </c>
+      <c r="AC11" s="6">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AD11" s="6">
+        <f t="shared" si="10"/>
+        <v>0.09160305344</v>
+      </c>
+      <c r="AE11" s="11"/>
+      <c r="AF11" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="AG11" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH11" s="20">
+        <f t="shared" ref="AH11:AL11" si="11">LN(X11)</f>
+        <v>-2.007468042</v>
+      </c>
+      <c r="AI11" s="20">
+        <f t="shared" si="11"/>
+        <v>-2.653241965</v>
+      </c>
+      <c r="AJ11" s="20">
+        <f t="shared" si="11"/>
+        <v>-1.922032305</v>
+      </c>
+      <c r="AK11" s="20">
+        <f t="shared" si="11"/>
+        <v>-2.756840365</v>
+      </c>
+      <c r="AL11" s="20">
+        <f t="shared" si="11"/>
+        <v>-3.349904087</v>
+      </c>
+      <c r="AM11" s="20">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AN11" s="20">
+        <f t="shared" si="13"/>
+        <v>-2.390290673</v>
+      </c>
+      <c r="AO11" s="11"/>
+      <c r="AP11" s="11"/>
+      <c r="AQ11" s="11"/>
+      <c r="AR11" s="11"/>
+      <c r="AS11" s="11"/>
+      <c r="AT11" s="11"/>
+      <c r="AU11" s="11"/>
+      <c r="AV11" s="11"/>
+      <c r="AW11" s="11"/>
+      <c r="AX11" s="11"/>
+      <c r="AY11" s="11"/>
+      <c r="AZ11" s="11"/>
+      <c r="BA11" s="11"/>
+      <c r="BB11" s="11"/>
+      <c r="BC11" s="11"/>
+      <c r="BD11" s="11"/>
+      <c r="BE11" s="11"/>
+      <c r="BF11" s="11"/>
+      <c r="BG11" s="11"/>
+      <c r="BH11" s="11"/>
+      <c r="BI11" s="11"/>
+      <c r="BJ11" s="11"/>
+      <c r="BK11" s="11"/>
+      <c r="BL11" s="11"/>
+      <c r="BM11" s="11"/>
+      <c r="BN11" s="11"/>
+      <c r="BO11" s="11"/>
+      <c r="BP11" s="11"/>
+      <c r="BQ11" s="11"/>
+      <c r="BR11" s="11"/>
+      <c r="BS11" s="11"/>
+      <c r="BT11" s="11"/>
+      <c r="BU11" s="11"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" s="6">
+        <v>6.0</v>
+      </c>
+      <c r="E12" s="15">
+        <f>180-30</f>
+        <v>150</v>
+      </c>
+      <c r="F12" s="6">
+        <v>60.0</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H12" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="I12" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="L12" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="M12" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="N12" s="6">
+        <v>6.0</v>
+      </c>
+      <c r="O12" s="15">
+        <f>180-30</f>
+        <v>150</v>
+      </c>
+      <c r="P12" s="6">
+        <f t="shared" si="2"/>
+        <v>0.01666666667</v>
+      </c>
+      <c r="Q12" s="6">
+        <f>1/E3</f>
+        <v>0.5</v>
+      </c>
+      <c r="R12" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="S12" s="6">
+        <f>1/I12</f>
+        <v>0.5</v>
+      </c>
+      <c r="T12" s="6">
+        <f>1/F6</f>
+        <v>0.3333333333</v>
+      </c>
+      <c r="V12" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="W12" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="X12" s="6">
+        <f t="shared" si="4"/>
+        <v>0.08955223881</v>
+      </c>
+      <c r="Y12" s="15">
+        <f t="shared" si="5"/>
+        <v>0.1408450704</v>
+      </c>
+      <c r="Z12" s="6">
+        <f t="shared" si="6"/>
+        <v>0.08534710018</v>
+      </c>
+      <c r="AA12" s="6">
+        <f t="shared" si="7"/>
+        <v>0.09523809524</v>
+      </c>
+      <c r="AB12" s="6">
+        <f t="shared" si="8"/>
+        <v>0.0350877193</v>
+      </c>
+      <c r="AC12" s="6">
+        <f t="shared" si="9"/>
+        <v>0.2333333333</v>
+      </c>
+      <c r="AD12" s="6">
+        <f t="shared" si="10"/>
+        <v>0.1526717557</v>
+      </c>
+      <c r="AE12" s="11"/>
+      <c r="AF12" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG12" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH12" s="20">
+        <f t="shared" ref="AH12:AL12" si="14">LN(X12)</f>
+        <v>-2.41293315</v>
+      </c>
+      <c r="AI12" s="20">
+        <f t="shared" si="14"/>
+        <v>-1.960094784</v>
+      </c>
+      <c r="AJ12" s="20">
+        <f t="shared" si="14"/>
+        <v>-2.461028806</v>
+      </c>
+      <c r="AK12" s="20">
+        <f t="shared" si="14"/>
+        <v>-2.351375257</v>
+      </c>
+      <c r="AL12" s="20">
+        <f t="shared" si="14"/>
+        <v>-3.349904087</v>
+      </c>
+      <c r="AM12" s="20">
+        <f t="shared" si="12"/>
+        <v>-1.455287233</v>
+      </c>
+      <c r="AN12" s="20">
+        <f t="shared" si="13"/>
+        <v>-1.87946505</v>
+      </c>
+      <c r="AO12" s="11"/>
+      <c r="AP12" s="11"/>
+      <c r="AQ12" s="11"/>
+      <c r="AR12" s="11"/>
+      <c r="AS12" s="11"/>
+      <c r="AT12" s="11"/>
+      <c r="AU12" s="11"/>
+      <c r="AV12" s="11"/>
+      <c r="AW12" s="11"/>
+      <c r="AX12" s="11"/>
+      <c r="AY12" s="11"/>
+      <c r="AZ12" s="11"/>
+      <c r="BA12" s="11"/>
+      <c r="BB12" s="11"/>
+      <c r="BC12" s="11"/>
+      <c r="BD12" s="11"/>
+      <c r="BE12" s="11"/>
+      <c r="BF12" s="11"/>
+      <c r="BG12" s="11"/>
+      <c r="BH12" s="11"/>
+      <c r="BI12" s="11"/>
+      <c r="BJ12" s="11"/>
+      <c r="BK12" s="11"/>
+      <c r="BL12" s="11"/>
+      <c r="BM12" s="11"/>
+      <c r="BN12" s="11"/>
+      <c r="BO12" s="11"/>
+      <c r="BP12" s="11"/>
+      <c r="BQ12" s="11"/>
+      <c r="BR12" s="11"/>
+      <c r="BS12" s="11"/>
+      <c r="BT12" s="11"/>
+      <c r="BU12" s="11"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="E13" s="15">
+        <f>220-52</f>
+        <v>168</v>
+      </c>
+      <c r="F13" s="6">
+        <v>60.0</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="H13" s="6">
+        <v>7.0</v>
+      </c>
+      <c r="I13" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="L13" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="M13" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="N13" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="O13" s="15">
+        <f>220-52</f>
+        <v>168</v>
+      </c>
+      <c r="P13" s="6">
+        <f t="shared" si="2"/>
+        <v>0.01666666667</v>
+      </c>
+      <c r="Q13" s="6">
+        <f>1/D3</f>
+        <v>1</v>
+      </c>
+      <c r="R13" s="6">
+        <v>7.0</v>
+      </c>
+      <c r="S13" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="T13" s="6">
+        <f t="shared" ref="T13:T15" si="16">1/$G$6</f>
+        <v>0.25</v>
+      </c>
+      <c r="V13" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="W13" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="X13" s="6">
+        <f t="shared" si="4"/>
+        <v>0.05970149254</v>
+      </c>
+      <c r="Y13" s="15">
+        <f t="shared" si="5"/>
+        <v>0.1577464789</v>
+      </c>
+      <c r="Z13" s="6">
+        <f t="shared" si="6"/>
+        <v>0.08534710018</v>
+      </c>
+      <c r="AA13" s="6">
+        <f t="shared" si="7"/>
+        <v>0.1904761905</v>
+      </c>
+      <c r="AB13" s="6">
+        <f t="shared" si="8"/>
+        <v>0.1228070175</v>
+      </c>
+      <c r="AC13" s="6">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AD13" s="6">
+        <f t="shared" si="10"/>
+        <v>0.1145038168</v>
+      </c>
+      <c r="AE13" s="11"/>
+      <c r="AF13" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="AG13" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="AH13" s="20">
+        <f t="shared" ref="AH13:AL13" si="15">LN(X13)</f>
+        <v>-2.818398258</v>
+      </c>
+      <c r="AI13" s="20">
+        <f t="shared" si="15"/>
+        <v>-1.846766099</v>
+      </c>
+      <c r="AJ13" s="20">
+        <f t="shared" si="15"/>
+        <v>-2.461028806</v>
+      </c>
+      <c r="AK13" s="20">
+        <f t="shared" si="15"/>
+        <v>-1.658228077</v>
+      </c>
+      <c r="AL13" s="20">
+        <f t="shared" si="15"/>
+        <v>-2.097141119</v>
+      </c>
+      <c r="AM13" s="20">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AN13" s="20">
+        <f t="shared" si="13"/>
+        <v>-2.167147122</v>
+      </c>
+      <c r="AO13" s="11"/>
+      <c r="AP13" s="11"/>
+      <c r="AQ13" s="11"/>
+      <c r="AR13" s="11"/>
+      <c r="AS13" s="11"/>
+      <c r="AT13" s="11"/>
+      <c r="AU13" s="11"/>
+      <c r="AV13" s="11"/>
+      <c r="AW13" s="11"/>
+      <c r="AX13" s="11"/>
+      <c r="AY13" s="11"/>
+      <c r="AZ13" s="11"/>
+      <c r="BA13" s="11"/>
+      <c r="BB13" s="11"/>
+      <c r="BC13" s="11"/>
+      <c r="BD13" s="11"/>
+      <c r="BE13" s="11"/>
+      <c r="BF13" s="11"/>
+      <c r="BG13" s="11"/>
+      <c r="BH13" s="11"/>
+      <c r="BI13" s="11"/>
+      <c r="BJ13" s="11"/>
+      <c r="BK13" s="11"/>
+      <c r="BL13" s="11"/>
+      <c r="BM13" s="11"/>
+      <c r="BN13" s="11"/>
+      <c r="BO13" s="11"/>
+      <c r="BP13" s="11"/>
+      <c r="BQ13" s="11"/>
+      <c r="BR13" s="11"/>
+      <c r="BS13" s="11"/>
+      <c r="BT13" s="11"/>
+      <c r="BU13" s="11"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" s="6">
+        <v>6.0</v>
+      </c>
+      <c r="E14" s="15">
+        <f>140 - 58</f>
+        <v>82</v>
+      </c>
+      <c r="F14" s="6">
+        <v>70.0</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="6">
+        <v>14.0</v>
+      </c>
+      <c r="I14" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="L14" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="M14" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="N14" s="6">
+        <v>6.0</v>
+      </c>
+      <c r="O14" s="15">
+        <f>140 - 58</f>
+        <v>82</v>
+      </c>
+      <c r="P14" s="6">
+        <f t="shared" si="2"/>
+        <v>0.01428571429</v>
+      </c>
+      <c r="Q14" s="6">
+        <f>1/F3</f>
+        <v>0.3333333333</v>
+      </c>
+      <c r="R14" s="6">
+        <v>14.0</v>
+      </c>
+      <c r="S14" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="T14" s="6">
+        <f t="shared" si="16"/>
+        <v>0.25</v>
+      </c>
+      <c r="V14" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="W14" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="X14" s="6">
+        <f t="shared" si="4"/>
+        <v>0.08955223881</v>
+      </c>
+      <c r="Y14" s="15">
+        <f t="shared" si="5"/>
+        <v>0.07699530516</v>
+      </c>
+      <c r="Z14" s="6">
+        <f t="shared" si="6"/>
+        <v>0.07315465729</v>
+      </c>
+      <c r="AA14" s="6">
+        <f t="shared" si="7"/>
+        <v>0.06349206349</v>
+      </c>
+      <c r="AB14" s="6">
+        <f t="shared" si="8"/>
+        <v>0.2456140351</v>
+      </c>
+      <c r="AC14" s="6">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AD14" s="6">
+        <f t="shared" si="10"/>
+        <v>0.1145038168</v>
+      </c>
+      <c r="AE14" s="11"/>
+      <c r="AF14" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="AG14" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="AH14" s="20">
+        <f t="shared" ref="AH14:AL14" si="17">LN(X14)</f>
+        <v>-2.41293315</v>
+      </c>
+      <c r="AI14" s="20">
+        <f t="shared" si="17"/>
+        <v>-2.564010831</v>
+      </c>
+      <c r="AJ14" s="20">
+        <f t="shared" si="17"/>
+        <v>-2.615179486</v>
+      </c>
+      <c r="AK14" s="20">
+        <f t="shared" si="17"/>
+        <v>-2.756840365</v>
+      </c>
+      <c r="AL14" s="20">
+        <f t="shared" si="17"/>
+        <v>-1.403993938</v>
+      </c>
+      <c r="AM14" s="20">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AN14" s="20">
+        <f t="shared" si="13"/>
+        <v>-2.167147122</v>
+      </c>
+      <c r="AO14" s="11"/>
+      <c r="AP14" s="11"/>
+      <c r="AQ14" s="11"/>
+      <c r="AR14" s="11"/>
+      <c r="AS14" s="11"/>
+      <c r="AT14" s="11"/>
+      <c r="AU14" s="11"/>
+      <c r="AV14" s="11"/>
+      <c r="AW14" s="11"/>
+      <c r="AX14" s="11"/>
+      <c r="AY14" s="11"/>
+      <c r="AZ14" s="11"/>
+      <c r="BA14" s="11"/>
+      <c r="BB14" s="11"/>
+      <c r="BC14" s="11"/>
+      <c r="BD14" s="11"/>
+      <c r="BE14" s="11"/>
+      <c r="BF14" s="11"/>
+      <c r="BG14" s="11"/>
+      <c r="BH14" s="11"/>
+      <c r="BI14" s="11"/>
+      <c r="BJ14" s="11"/>
+      <c r="BK14" s="11"/>
+      <c r="BL14" s="11"/>
+      <c r="BM14" s="11"/>
+      <c r="BN14" s="11"/>
+      <c r="BO14" s="11"/>
+      <c r="BP14" s="11"/>
+      <c r="BQ14" s="11"/>
+      <c r="BR14" s="11"/>
+      <c r="BS14" s="11"/>
+      <c r="BT14" s="11"/>
+      <c r="BU14" s="11"/>
+    </row>
+    <row r="15">
+      <c r="B15" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" s="6">
+        <v>6.0</v>
+      </c>
+      <c r="E15" s="15">
+        <f>140 - 54</f>
+        <v>86</v>
+      </c>
+      <c r="F15" s="6">
+        <v>70.0</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H15" s="6">
+        <v>14.0</v>
+      </c>
+      <c r="I15" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="L15" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="M15" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="N15" s="6">
+        <v>6.0</v>
+      </c>
+      <c r="O15" s="15">
+        <f>140 - 54</f>
+        <v>86</v>
+      </c>
+      <c r="P15" s="6">
+        <f t="shared" si="2"/>
+        <v>0.01428571429</v>
+      </c>
+      <c r="Q15" s="6">
+        <f>1/F3</f>
+        <v>0.3333333333</v>
+      </c>
+      <c r="R15" s="6">
+        <v>14.0</v>
+      </c>
+      <c r="S15" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="T15" s="6">
+        <f t="shared" si="16"/>
+        <v>0.25</v>
+      </c>
+      <c r="V15" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="W15" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="X15" s="6">
+        <f t="shared" si="4"/>
+        <v>0.08955223881</v>
+      </c>
+      <c r="Y15" s="15">
+        <f t="shared" si="5"/>
+        <v>0.08075117371</v>
+      </c>
+      <c r="Z15" s="6">
+        <f t="shared" si="6"/>
+        <v>0.07315465729</v>
+      </c>
+      <c r="AA15" s="6">
+        <f t="shared" si="7"/>
+        <v>0.06349206349</v>
+      </c>
+      <c r="AB15" s="6">
+        <f t="shared" si="8"/>
+        <v>0.2456140351</v>
+      </c>
+      <c r="AC15" s="6">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AD15" s="6">
+        <f t="shared" si="10"/>
+        <v>0.1145038168</v>
+      </c>
+      <c r="AE15" s="11"/>
+      <c r="AF15" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="AG15" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH15" s="20">
+        <f t="shared" ref="AH15:AL15" si="18">LN(X15)</f>
+        <v>-2.41293315</v>
+      </c>
+      <c r="AI15" s="20">
+        <f t="shared" si="18"/>
+        <v>-2.516382782</v>
+      </c>
+      <c r="AJ15" s="20">
+        <f t="shared" si="18"/>
+        <v>-2.615179486</v>
+      </c>
+      <c r="AK15" s="20">
+        <f t="shared" si="18"/>
+        <v>-2.756840365</v>
+      </c>
+      <c r="AL15" s="20">
+        <f t="shared" si="18"/>
+        <v>-1.403993938</v>
+      </c>
+      <c r="AM15" s="20">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AN15" s="20">
+        <f t="shared" si="13"/>
+        <v>-2.167147122</v>
+      </c>
+      <c r="AO15" s="11"/>
+      <c r="AP15" s="11"/>
+      <c r="AQ15" s="11"/>
+      <c r="AR15" s="11"/>
+      <c r="AS15" s="11"/>
+      <c r="AT15" s="11"/>
+      <c r="AU15" s="11"/>
+      <c r="AV15" s="11"/>
+      <c r="AW15" s="11"/>
+      <c r="AX15" s="11"/>
+      <c r="AY15" s="11"/>
+      <c r="AZ15" s="11"/>
+      <c r="BA15" s="11"/>
+      <c r="BB15" s="11"/>
+      <c r="BC15" s="11"/>
+      <c r="BD15" s="11"/>
+      <c r="BE15" s="11"/>
+      <c r="BF15" s="11"/>
+      <c r="BG15" s="11"/>
+      <c r="BH15" s="11"/>
+      <c r="BI15" s="11"/>
+      <c r="BJ15" s="11"/>
+      <c r="BK15" s="11"/>
+      <c r="BL15" s="11"/>
+      <c r="BM15" s="11"/>
+      <c r="BN15" s="11"/>
+      <c r="BO15" s="11"/>
+      <c r="BP15" s="11"/>
+      <c r="BQ15" s="11"/>
+      <c r="BR15" s="11"/>
+      <c r="BS15" s="11"/>
+      <c r="BT15" s="11"/>
+      <c r="BU15" s="11"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="6">
+        <v>6.0</v>
+      </c>
+      <c r="E16" s="15">
+        <f>155-31</f>
+        <v>124</v>
+      </c>
+      <c r="F16" s="6">
+        <v>30.0</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="H16" s="6">
+        <v>7.0</v>
+      </c>
+      <c r="I16" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="L16" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="M16" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="N16" s="6">
+        <v>6.0</v>
+      </c>
+      <c r="O16" s="15">
+        <f>155-31</f>
+        <v>124</v>
+      </c>
+      <c r="P16" s="6">
+        <f t="shared" si="2"/>
+        <v>0.03333333333</v>
+      </c>
+      <c r="Q16" s="6">
+        <f>1/D3</f>
+        <v>1</v>
+      </c>
+      <c r="R16" s="6">
+        <v>7.0</v>
+      </c>
+      <c r="S16" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="T16" s="6">
+        <f>1/$H$6</f>
+        <v>0.2</v>
+      </c>
+      <c r="V16" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="W16" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="X16" s="6">
+        <f t="shared" si="4"/>
+        <v>0.08955223881</v>
+      </c>
+      <c r="Y16" s="15">
+        <f t="shared" si="5"/>
+        <v>0.1164319249</v>
+      </c>
+      <c r="Z16" s="6">
+        <f t="shared" si="6"/>
+        <v>0.1706942004</v>
+      </c>
+      <c r="AA16" s="6">
+        <f t="shared" si="7"/>
+        <v>0.1904761905</v>
+      </c>
+      <c r="AB16" s="6">
+        <f t="shared" si="8"/>
+        <v>0.1228070175</v>
+      </c>
+      <c r="AC16" s="6">
+        <f t="shared" si="9"/>
+        <v>0.4666666667</v>
+      </c>
+      <c r="AD16" s="6">
+        <f t="shared" si="10"/>
+        <v>0.09160305344</v>
+      </c>
+      <c r="AE16" s="11"/>
+      <c r="AF16" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="AG16" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="AH16" s="20">
+        <f t="shared" ref="AH16:AL16" si="19">LN(X16)</f>
+        <v>-2.41293315</v>
+      </c>
+      <c r="AI16" s="20">
+        <f t="shared" si="19"/>
+        <v>-2.150448513</v>
+      </c>
+      <c r="AJ16" s="20">
+        <f t="shared" si="19"/>
+        <v>-1.767881625</v>
+      </c>
+      <c r="AK16" s="20">
+        <f t="shared" si="19"/>
+        <v>-1.658228077</v>
+      </c>
+      <c r="AL16" s="20">
+        <f t="shared" si="19"/>
+        <v>-2.097141119</v>
+      </c>
+      <c r="AM16" s="20">
+        <f t="shared" si="12"/>
+        <v>-0.762140052</v>
+      </c>
+      <c r="AN16" s="20">
+        <f t="shared" si="13"/>
+        <v>-2.390290673</v>
+      </c>
+      <c r="AO16" s="11"/>
+      <c r="AP16" s="11"/>
+      <c r="AQ16" s="11"/>
+      <c r="AR16" s="11"/>
+      <c r="AS16" s="11"/>
+      <c r="AT16" s="11"/>
+      <c r="AU16" s="11"/>
+      <c r="AV16" s="11"/>
+      <c r="AW16" s="11"/>
+      <c r="AX16" s="11"/>
+      <c r="AY16" s="11"/>
+      <c r="AZ16" s="11"/>
+      <c r="BA16" s="11"/>
+      <c r="BB16" s="11"/>
+      <c r="BC16" s="11"/>
+      <c r="BD16" s="11"/>
+      <c r="BE16" s="11"/>
+      <c r="BF16" s="11"/>
+      <c r="BG16" s="11"/>
+      <c r="BH16" s="11"/>
+      <c r="BI16" s="11"/>
+      <c r="BJ16" s="11"/>
+      <c r="BK16" s="11"/>
+      <c r="BL16" s="11"/>
+      <c r="BM16" s="11"/>
+      <c r="BN16" s="11"/>
+      <c r="BO16" s="11"/>
+      <c r="BP16" s="11"/>
+      <c r="BQ16" s="11"/>
+      <c r="BR16" s="11"/>
+      <c r="BS16" s="11"/>
+      <c r="BT16" s="11"/>
+      <c r="BU16" s="11"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" s="6">
+        <v>6.0</v>
+      </c>
+      <c r="E17" s="15">
+        <f>220-67</f>
+        <v>153</v>
+      </c>
+      <c r="F17" s="6">
+        <v>37.0</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H17" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="I17" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="L17" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="M17" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="N17" s="6">
+        <v>6.0</v>
+      </c>
+      <c r="O17" s="15">
+        <f>220-67</f>
+        <v>153</v>
+      </c>
+      <c r="P17" s="6">
+        <f t="shared" si="2"/>
+        <v>0.02702702703</v>
+      </c>
+      <c r="Q17" s="6">
+        <f>1/E3</f>
+        <v>0.5</v>
+      </c>
+      <c r="R17" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="S17" s="6">
+        <f>1/I17</f>
+        <v>0.5</v>
+      </c>
+      <c r="T17" s="6">
+        <f t="shared" ref="T17:T18" si="21">1/$G$6</f>
+        <v>0.25</v>
+      </c>
+      <c r="V17" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="W17" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="X17" s="6">
+        <f t="shared" si="4"/>
+        <v>0.08955223881</v>
+      </c>
+      <c r="Y17" s="15">
+        <f t="shared" si="5"/>
+        <v>0.1436619718</v>
+      </c>
+      <c r="Z17" s="6">
+        <f t="shared" si="6"/>
+        <v>0.138400703</v>
+      </c>
+      <c r="AA17" s="6">
+        <f t="shared" si="7"/>
+        <v>0.09523809524</v>
+      </c>
+      <c r="AB17" s="6">
+        <f t="shared" si="8"/>
+        <v>0.0701754386</v>
+      </c>
+      <c r="AC17" s="6">
+        <f t="shared" si="9"/>
+        <v>0.2333333333</v>
+      </c>
+      <c r="AD17" s="6">
+        <f t="shared" si="10"/>
+        <v>0.1145038168</v>
+      </c>
+      <c r="AE17" s="11"/>
+      <c r="AF17" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="AG17" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="AH17" s="20">
+        <f t="shared" ref="AH17:AL17" si="20">LN(X17)</f>
+        <v>-2.41293315</v>
+      </c>
+      <c r="AI17" s="20">
+        <f t="shared" si="20"/>
+        <v>-1.940292157</v>
+      </c>
+      <c r="AJ17" s="20">
+        <f t="shared" si="20"/>
+        <v>-1.977602156</v>
+      </c>
+      <c r="AK17" s="20">
+        <f t="shared" si="20"/>
+        <v>-2.351375257</v>
+      </c>
+      <c r="AL17" s="20">
+        <f t="shared" si="20"/>
+        <v>-2.656756907</v>
+      </c>
+      <c r="AM17" s="20">
+        <f t="shared" si="12"/>
+        <v>-1.455287233</v>
+      </c>
+      <c r="AN17" s="20">
+        <f t="shared" si="13"/>
+        <v>-2.167147122</v>
+      </c>
+      <c r="AO17" s="11"/>
+      <c r="AP17" s="11"/>
+      <c r="AQ17" s="11"/>
+      <c r="AR17" s="11"/>
+      <c r="AS17" s="11"/>
+      <c r="AT17" s="11"/>
+      <c r="AU17" s="11"/>
+      <c r="AV17" s="11"/>
+      <c r="AW17" s="11"/>
+      <c r="AX17" s="11"/>
+      <c r="AY17" s="11"/>
+      <c r="AZ17" s="11"/>
+      <c r="BA17" s="11"/>
+      <c r="BB17" s="11"/>
+      <c r="BC17" s="11"/>
+      <c r="BD17" s="11"/>
+      <c r="BE17" s="11"/>
+      <c r="BF17" s="11"/>
+      <c r="BG17" s="11"/>
+      <c r="BH17" s="11"/>
+      <c r="BI17" s="11"/>
+      <c r="BJ17" s="11"/>
+      <c r="BK17" s="11"/>
+      <c r="BL17" s="11"/>
+      <c r="BM17" s="11"/>
+      <c r="BN17" s="11"/>
+      <c r="BO17" s="11"/>
+      <c r="BP17" s="11"/>
+      <c r="BQ17" s="11"/>
+      <c r="BR17" s="11"/>
+      <c r="BS17" s="11"/>
+      <c r="BT17" s="11"/>
+      <c r="BU17" s="11"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" s="6">
+        <v>6.0</v>
+      </c>
+      <c r="E18" s="6">
+        <f>220-51</f>
+        <v>169</v>
+      </c>
+      <c r="F18" s="6">
+        <v>90.0</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="H18" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="I18" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="L18" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="M18" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="N18" s="6">
+        <v>6.0</v>
+      </c>
+      <c r="O18" s="6">
+        <f>220-51</f>
+        <v>169</v>
+      </c>
+      <c r="P18" s="6">
+        <f t="shared" si="2"/>
+        <v>0.01111111111</v>
+      </c>
+      <c r="Q18" s="6">
+        <f>1/G3</f>
+        <v>0.25</v>
+      </c>
+      <c r="R18" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="S18" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="T18" s="6">
+        <f t="shared" si="21"/>
+        <v>0.25</v>
+      </c>
+      <c r="V18" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="W18" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="X18" s="6">
+        <f t="shared" si="4"/>
+        <v>0.08955223881</v>
+      </c>
+      <c r="Y18" s="15">
+        <f t="shared" si="5"/>
+        <v>0.158685446</v>
+      </c>
+      <c r="Z18" s="6">
+        <f t="shared" si="6"/>
+        <v>0.05689806678</v>
+      </c>
+      <c r="AA18" s="6">
+        <f t="shared" si="7"/>
+        <v>0.04761904762</v>
+      </c>
+      <c r="AB18" s="6">
+        <f t="shared" si="8"/>
+        <v>0.08771929825</v>
+      </c>
+      <c r="AC18" s="6">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AD18" s="6">
+        <f t="shared" si="10"/>
+        <v>0.1145038168</v>
+      </c>
+      <c r="AE18" s="11"/>
+      <c r="AF18" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="AG18" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="AH18" s="20">
+        <f t="shared" ref="AH18:AL18" si="22">LN(X18)</f>
+        <v>-2.41293315</v>
+      </c>
+      <c r="AI18" s="20">
+        <f t="shared" si="22"/>
+        <v>-1.840831363</v>
+      </c>
+      <c r="AJ18" s="20">
+        <f t="shared" si="22"/>
+        <v>-2.866493914</v>
+      </c>
+      <c r="AK18" s="20">
+        <f t="shared" si="22"/>
+        <v>-3.044522438</v>
+      </c>
+      <c r="AL18" s="20">
+        <f t="shared" si="22"/>
+        <v>-2.433613355</v>
+      </c>
+      <c r="AM18" s="20">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AN18" s="20">
+        <f t="shared" si="13"/>
+        <v>-2.167147122</v>
+      </c>
+      <c r="AO18" s="11"/>
+      <c r="AP18" s="11"/>
+      <c r="AQ18" s="11"/>
+      <c r="AR18" s="11"/>
+      <c r="AS18" s="11"/>
+      <c r="AT18" s="11"/>
+      <c r="AU18" s="11"/>
+      <c r="AV18" s="11"/>
+      <c r="AW18" s="11"/>
+      <c r="AX18" s="11"/>
+      <c r="AY18" s="11"/>
+      <c r="AZ18" s="11"/>
+      <c r="BA18" s="11"/>
+      <c r="BB18" s="11"/>
+      <c r="BC18" s="11"/>
+      <c r="BD18" s="11"/>
+      <c r="BE18" s="11"/>
+      <c r="BF18" s="11"/>
+      <c r="BG18" s="11"/>
+      <c r="BH18" s="11"/>
+      <c r="BI18" s="11"/>
+      <c r="BJ18" s="11"/>
+      <c r="BK18" s="11"/>
+      <c r="BL18" s="11"/>
+      <c r="BM18" s="11"/>
+      <c r="BN18" s="11"/>
+      <c r="BO18" s="11"/>
+      <c r="BP18" s="11"/>
+      <c r="BQ18" s="11"/>
+      <c r="BR18" s="11"/>
+      <c r="BS18" s="11"/>
+      <c r="BT18" s="11"/>
+      <c r="BU18" s="11"/>
+    </row>
+    <row r="19">
+      <c r="M19" s="35" t="s">
+        <v>63</v>
+      </c>
+      <c r="N19" s="36">
+        <f t="shared" ref="N19:T19" si="23">SUM(N10:N18)</f>
+        <v>67</v>
+      </c>
+      <c r="O19" s="36">
+        <f t="shared" si="23"/>
+        <v>1065</v>
+      </c>
+      <c r="P19" s="36">
+        <f t="shared" si="23"/>
+        <v>0.1952809953</v>
+      </c>
+      <c r="Q19" s="36">
+        <f t="shared" si="23"/>
+        <v>5.25</v>
+      </c>
+      <c r="R19" s="36">
+        <f t="shared" si="23"/>
+        <v>57</v>
+      </c>
+      <c r="S19" s="36">
+        <f t="shared" si="23"/>
+        <v>2.142857143</v>
+      </c>
+      <c r="T19" s="36">
+        <f t="shared" si="23"/>
+        <v>2.183333333</v>
+      </c>
+      <c r="AG19" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="AH19" s="37">
+        <f t="shared" ref="AH19:AN19" si="24">$AH$22*SUMPRODUCT(AH10:AH18,X10:X18)</f>
+        <v>-1.072775632</v>
+      </c>
+      <c r="AI19" s="37">
+        <f t="shared" si="24"/>
+        <v>-1.096962742</v>
+      </c>
+      <c r="AJ19" s="37">
+        <f t="shared" si="24"/>
+        <v>-1.091650333</v>
+      </c>
+      <c r="AK19" s="37">
+        <f t="shared" si="24"/>
+        <v>-1.061472244</v>
+      </c>
+      <c r="AL19" s="37">
+        <f t="shared" si="24"/>
+        <v>-1.005855253</v>
+      </c>
+      <c r="AM19" s="37">
+        <f t="shared" si="24"/>
+        <v>-0.6245591967</v>
+      </c>
+      <c r="AN19" s="37">
+        <f t="shared" si="24"/>
+        <v>-1.122635641</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="AG20" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="AH20" s="37">
+        <f t="shared" ref="AH20:AN20" si="25">1-AH19</f>
+        <v>2.072775632</v>
+      </c>
+      <c r="AI20" s="37">
+        <f t="shared" si="25"/>
+        <v>2.096962742</v>
+      </c>
+      <c r="AJ20" s="37">
+        <f t="shared" si="25"/>
+        <v>2.091650333</v>
+      </c>
+      <c r="AK20" s="37">
+        <f t="shared" si="25"/>
+        <v>2.061472244</v>
+      </c>
+      <c r="AL20" s="37">
+        <f t="shared" si="25"/>
+        <v>2.005855253</v>
+      </c>
+      <c r="AM20" s="37">
+        <f t="shared" si="25"/>
+        <v>1.624559197</v>
+      </c>
+      <c r="AN20" s="37">
+        <f t="shared" si="25"/>
+        <v>2.122635641</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="AG21" s="35" t="s">
+        <v>83</v>
+      </c>
+      <c r="AH21" s="39">
+        <f t="shared" ref="AH21:AN21" si="26">AH20/SUM($AH$20:$AN$20)</f>
+        <v>0.1472569432</v>
+      </c>
+      <c r="AI21" s="39">
+        <f t="shared" si="26"/>
+        <v>0.1489752767</v>
+      </c>
+      <c r="AJ21" s="39">
+        <f t="shared" si="26"/>
+        <v>0.1485978653</v>
+      </c>
+      <c r="AK21" s="39">
+        <f t="shared" si="26"/>
+        <v>0.1464539125</v>
+      </c>
+      <c r="AL21" s="39">
+        <f t="shared" si="26"/>
+        <v>0.1425026946</v>
+      </c>
+      <c r="AM21" s="39">
+        <f t="shared" si="26"/>
+        <v>0.1154141421</v>
+      </c>
+      <c r="AN21" s="39">
+        <f t="shared" si="26"/>
+        <v>0.1507991656</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="AG22" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH22" s="37">
+        <f>1/LN(AJ22)</f>
+        <v>0.5138983424</v>
+      </c>
+      <c r="AI22" s="40" t="s">
+        <v>85</v>
+      </c>
+      <c r="AJ22" s="20">
+        <v>7.0</v>
+      </c>
+      <c r="AK22" s="41"/>
+      <c r="AL22" s="41"/>
+      <c r="AM22" s="41"/>
+      <c r="AN22" s="41"/>
+    </row>
+    <row r="23">
+      <c r="AH23" s="41"/>
+      <c r="AI23" s="41"/>
+      <c r="AJ23" s="41"/>
+      <c r="AK23" s="41"/>
+      <c r="AL23" s="41"/>
+      <c r="AM23" s="41"/>
+      <c r="AN23" s="41"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="B8:C9"/>
+    <mergeCell ref="L8:M9"/>
+    <mergeCell ref="V8:W9"/>
+    <mergeCell ref="AF8:AG9"/>
+  </mergeCells>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>